--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -62871,18 +62871,41 @@
         <v>510</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.35699999332428</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.351000010967255</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.351999998092651</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="F2718" t="n">
         <v>0.344999998807907</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.351000010967255</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.342999994754791</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.351000010967255</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>26700</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.342999994754791</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.342000007629395</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>17142</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3376</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.34799998998642</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.337000012397766</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.34799998998642</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>2098</v>
+        <v>1875</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.35699999332428</v>
+        <v>0.361000001430511</v>
       </c>
       <c r="D2715" t="n">
         <v>0.351999998092651</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.351999998092651</v>
+        <v>0.361000001430511</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.35699999332428</v>
+        <v>0.361000001430511</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,19 +62819,19 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>5</v>
+        <v>2098</v>
       </c>
       <c r="C2716" t="n">
         <v>0.35699999332428</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.35699999332428</v>
+        <v>0.351999998092651</v>
       </c>
       <c r="E2716" t="n">
-        <v>0.35699999332428</v>
+        <v>0.351999998092651</v>
       </c>
       <c r="F2716" t="n">
         <v>0.35699999332428</v>
@@ -62842,16 +62842,16 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>6842</v>
+        <v>5</v>
       </c>
       <c r="C2717" t="n">
         <v>0.35699999332428</v>
       </c>
       <c r="D2717" t="n">
-        <v>0.351000010967255</v>
+        <v>0.35699999332428</v>
       </c>
       <c r="E2717" t="n">
         <v>0.35699999332428</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>510</v>
+        <v>6842</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.344999998807907</v>
+        <v>0.35699999332428</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.344999998807907</v>
+        <v>0.351000010967255</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.344999998807907</v>
+        <v>0.35699999332428</v>
       </c>
       <c r="F2718" t="n">
-        <v>0.344999998807907</v>
+        <v>0.35699999332428</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>4775</v>
+        <v>510</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.351000010967255</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="D2719" t="n">
-        <v>0.342999994754791</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.345999985933304</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="F2719" t="n">
-        <v>0.351000010967255</v>
+        <v>0.344999998807907</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>26700</v>
+        <v>4775</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.349999994039536</v>
+        <v>0.351000010967255</v>
       </c>
       <c r="D2720" t="n">
-        <v>0.32600000500679</v>
+        <v>0.342999994754791</v>
       </c>
       <c r="E2720" t="n">
-        <v>0.342999994754791</v>
+        <v>0.345999985933304</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.342000007629395</v>
+        <v>0.351000010967255</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>17142</v>
+        <v>26700</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.345999985933304</v>
+        <v>0.349999994039536</v>
       </c>
       <c r="D2721" t="n">
         <v>0.32600000500679</v>
       </c>
       <c r="E2721" t="n">
-        <v>0.32600000500679</v>
+        <v>0.342999994754791</v>
       </c>
       <c r="F2721" t="n">
-        <v>0.345999985933304</v>
+        <v>0.342000007629395</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3376</v>
+        <v>17142</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.34799998998642</v>
+        <v>0.345999985933304</v>
       </c>
       <c r="D2722" t="n">
-        <v>0.335999995470047</v>
+        <v>0.32600000500679</v>
       </c>
       <c r="E2722" t="n">
-        <v>0.337000012397766</v>
+        <v>0.32600000500679</v>
       </c>
       <c r="F2722" t="n">
-        <v>0.34799998998642</v>
+        <v>0.345999985933304</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125348091125</v>
+        <v>2.38125371932983</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652428627014</v>
+        <v>2.29652404785156</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419295310974</v>
+        <v>2.37419271469116</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771513938904</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34948015213013</v>
+        <v>2.34947991371155</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595796585083</v>
+        <v>2.37595820426941</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828953742981</v>
+        <v>2.29828929901123</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123708724976</v>
+        <v>2.32123684883118</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299378395081</v>
+        <v>2.29299354553223</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22415089607239</v>
+        <v>2.22415065765381</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062894821167</v>
+        <v>2.25062870979309</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181100845337</v>
+        <v>2.27181124687195</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475879669189</v>
+        <v>2.29475903511047</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236021995544</v>
+        <v>2.1323606967926</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412594795227</v>
+        <v>2.13412547111511</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230200767517</v>
+        <v>1.92230176925659</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637328624725</v>
+        <v>1.75637316703796</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08293461799622</v>
+        <v>2.08293485641479</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.15354299545288</v>
+        <v>2.1535427570343</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413426399231</v>
+        <v>2.16413402557373</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177798271179</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824748039246</v>
+        <v>2.14824724197388</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300233840942</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542562484741</v>
+        <v>2.57542538642883</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953052520752</v>
+        <v>2.52953028678894</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.59484267234802</v>
+        <v>2.5948429107666</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723245620728</v>
+        <v>2.72723269462585</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841382026672</v>
+        <v>2.47841358184814</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998668670654</v>
+        <v>2.45998692512512</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544834136963</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913381576538</v>
+        <v>2.25913405418396</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097679138184</v>
+        <v>2.26097655296326</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385336875916</v>
+        <v>2.20385313034058</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070715904236</v>
+        <v>2.24070692062378</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517942428589</v>
+        <v>2.23517918586731</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731318473816</v>
+        <v>2.32731366157532</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338066101074</v>
+        <v>2.37338042259216</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785268783569</v>
+        <v>2.36785244941711</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547044754028</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915592193604</v>
+        <v>2.32915616035461</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396389961243</v>
+        <v>2.55396413803101</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477279663086</v>
+        <v>2.61477255821228</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68848013877869</v>
+        <v>2.68847990036011</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5465931892395</v>
+        <v>2.54659295082092</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061437606812</v>
+        <v>2.78061413764954</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349119186401</v>
+        <v>2.72349143028259</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456924438477</v>
+        <v>2.80456900596619</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879374504089</v>
+        <v>2.84879350662231</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.9151303768158</v>
+        <v>2.91513061523438</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515248298645</v>
+        <v>2.98515272140503</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097219467163</v>
+        <v>3.08097243309021</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2689266204834</v>
+        <v>3.26892638206482</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993811607361</v>
+        <v>3.13993835449219</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461345672607</v>
+        <v>2.94461369514465</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.99068069458008</v>
+        <v>2.9906804561615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05886006355286</v>
+        <v>3.05885982513428</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470164299011</v>
+        <v>3.22470188140869</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099430084229</v>
+        <v>3.15099453926086</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441014289856</v>
+        <v>3.13441038131714</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>0.345999985933304</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>4584</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.333999991416931</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.333999991416931</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478422164917</v>
+        <v>2.38478398323059</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125371932983</v>
+        <v>2.38125348091125</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419271469116</v>
+        <v>2.37419295310974</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771513938904</v>
+        <v>2.34771466255188</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34947991371155</v>
+        <v>2.34948015213013</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595820426941</v>
+        <v>2.37595772743225</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123684883118</v>
+        <v>2.32123708724976</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299354553223</v>
+        <v>2.29299402236938</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22415065765381</v>
+        <v>2.22415089607239</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062870979309</v>
+        <v>2.25062894821167</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003791809082</v>
+        <v>2.24003767967224</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28063726425171</v>
+        <v>2.28063750267029</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475903511047</v>
+        <v>2.29475879669189</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1323606967926</v>
+        <v>2.13236045837402</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884682655334</v>
+        <v>2.18884706497192</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120358467102</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1782557964325</v>
+        <v>2.17825555801392</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412547111511</v>
+        <v>2.13412594795227</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.9858490228653</v>
+        <v>1.98584914207458</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230176925659</v>
+        <v>1.92230188846588</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991198539734</v>
+        <v>1.78991210460663</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08293485641479</v>
+        <v>2.08293509483337</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120358467102</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351804733276</v>
+        <v>2.06351780891418</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413402557373</v>
+        <v>2.16413426399231</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177774429321</v>
+        <v>2.15177750587463</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824724197388</v>
+        <v>2.14824748039246</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.1270649433136</v>
+        <v>2.12706518173218</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530800819397</v>
+        <v>2.15530824661255</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296004295349</v>
+        <v>2.17296028137207</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828098297119</v>
+        <v>2.26828074455261</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300233840942</v>
+        <v>2.32300209999084</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953028678894</v>
+        <v>2.52953052520752</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.5948429107666</v>
+        <v>2.59484267234802</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664190292358</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664190292358</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192862510681</v>
+        <v>2.69192886352539</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369450569153</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789666175842</v>
+        <v>2.50789642333984</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605392456055</v>
+        <v>2.50605416297913</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48762702941895</v>
+        <v>2.48762726783752</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>2.48762702941895</v>
+        <v>2.48762726783752</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998692512512</v>
+        <v>2.45998668670654</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099865913391</v>
+        <v>2.33099889755249</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G121" t="n">
-        <v>2.34205508232117</v>
+        <v>2.34205484390259</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753884315491</v>
+        <v>2.20753860473633</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544857978821</v>
+        <v>2.25544881820679</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913405418396</v>
+        <v>2.25913381576538</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252779006958</v>
+        <v>2.17252802848816</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G147" t="n">
-        <v>2.31994247436523</v>
+        <v>2.31994271278381</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.43418908119202</v>
+        <v>2.4341893196106</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102100372314</v>
+        <v>2.40102076530457</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G163" t="n">
-        <v>2.31994247436523</v>
+        <v>2.31994271278381</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>2.31441473960876</v>
+        <v>2.31441450119019</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099865913391</v>
+        <v>2.33099889755249</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888628959656</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385313034058</v>
+        <v>2.20385336875916</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070692062378</v>
+        <v>2.24070715904236</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G193" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37706589698792</v>
+        <v>2.37706565856934</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731366157532</v>
+        <v>2.32731342315674</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391944885254</v>
+        <v>2.41391968727112</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888628959656</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547044754028</v>
+        <v>2.32547068595886</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965121269226</v>
+        <v>2.22965097427368</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G243" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G244" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>2.37706589698792</v>
+        <v>2.37706565856934</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391944885254</v>
+        <v>2.41391968727112</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G258" t="n">
-        <v>2.56501984596252</v>
+        <v>2.5650200843811</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G259" t="n">
-        <v>2.56317734718323</v>
+        <v>2.56317710876465</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396413803101</v>
+        <v>2.55396389961243</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76402997970581</v>
+        <v>2.76403021812439</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68847990036011</v>
+        <v>2.68848013877869</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.6442551612854</v>
+        <v>2.64425539970398</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>2.5668625831604</v>
+        <v>2.56686282157898</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657108306885</v>
+        <v>2.47657084465027</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369450569153</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G288" t="n">
-        <v>2.55764937400818</v>
+        <v>2.5576491355896</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349143028259</v>
+        <v>2.72349095344543</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>2.69032287597656</v>
+        <v>2.69032263755798</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G298" t="n">
-        <v>2.71059226989746</v>
+        <v>2.71059203147888</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76402997970581</v>
+        <v>2.76403021812439</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616445541382</v>
+        <v>2.85616421699524</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G308" t="n">
-        <v>2.81746816635132</v>
+        <v>2.8174684047699</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456900596619</v>
+        <v>2.80456924438477</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879350662231</v>
+        <v>2.84879374504089</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780411720276</v>
+        <v>3.04780387878418</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.27076888084412</v>
+        <v>3.2707691192627</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937722206116</v>
+        <v>3.02937698364258</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.0072648525238</v>
+        <v>3.00726461410522</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461369514465</v>
+        <v>2.94461345672607</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.9906804561615</v>
+        <v>2.99068069458008</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964661598206</v>
+        <v>3.04964637756348</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05885982513428</v>
+        <v>3.05886006355286</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045527458191</v>
+        <v>3.11045503616333</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03674793243408</v>
+        <v>3.0367476940155</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G353" t="n">
-        <v>2.98330974578857</v>
+        <v>2.98330998420715</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>3.04043316841125</v>
+        <v>3.04043292999268</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.2676408290863</v>
+        <v>3.26764059066772</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215264320374</v>
+        <v>3.29215288162231</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279147148132</v>
+        <v>3.18279123306274</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713475227356</v>
+        <v>3.17713451385498</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491179466248</v>
+        <v>3.11491203308105</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.9225869178772</v>
+        <v>2.92258667945862</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669528961182</v>
+        <v>2.98669505119324</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864707946777</v>
+        <v>2.88864684104919</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332790374756</v>
+        <v>2.94332766532898</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.8283097743988</v>
+        <v>2.82831001281738</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682827949524</v>
+        <v>2.78682804107666</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002665519714</v>
+        <v>2.80002689361572</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517753601074</v>
+        <v>2.71517777442932</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046611785889</v>
+        <v>2.99046635627747</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228563308716</v>
+        <v>3.09228539466858</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.0790867805481</v>
+        <v>3.07908654212952</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928566932678</v>
+        <v>2.77928590774536</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.45497298240662</v>
+        <v>2.4549732208252</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187652587891</v>
+        <v>2.57187628746033</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238236427307</v>
+        <v>2.66238212585449</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032793998718</v>
+        <v>2.63032817840576</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.5021116733551</v>
+        <v>2.50211143493652</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891282081604</v>
+        <v>2.48891258239746</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137068748474</v>
+        <v>2.48137044906616</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217804908752</v>
+        <v>2.40217781066895</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.52473783493042</v>
+        <v>2.524738073349</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399684906006</v>
+        <v>2.50399708747864</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834036827087</v>
+        <v>2.49834060668945</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005701065063</v>
+        <v>2.47005724906921</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520789146423</v>
+        <v>2.38520812988281</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.290931224823</v>
+        <v>2.29093098640442</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207565307617</v>
+        <v>2.27207589149475</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264810562134</v>
+        <v>2.26264786720276</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066029548645</v>
+        <v>2.13066005706787</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038900852203</v>
+        <v>1.97038924694061</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082599639893</v>
+        <v>1.88082611560822</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -71236,7 +71236,7 @@
         <v>0.345999985933304</v>
       </c>
       <c r="D2726" t="n">
-        <v>0.345999985933304</v>
+        <v>0.333999991416931</v>
       </c>
       <c r="E2726" t="n">
         <v>0.345999985933304</v>
@@ -71248,6 +71248,32 @@
         <v>0.333999991416931</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>7104</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.345999985933304</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.344999998807907</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.344999998807907</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478398323059</v>
+        <v>2.38478422164917</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182787895203</v>
+        <v>2.33182811737061</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652404785156</v>
+        <v>2.29652428627014</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595772743225</v>
+        <v>2.37595796585083</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828929901123</v>
+        <v>2.29828953742981</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299402236938</v>
+        <v>2.29299378395081</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181124687195</v>
+        <v>2.27181100845337</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003767967224</v>
+        <v>2.24003791809082</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28063750267029</v>
+        <v>2.28063726425171</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236045837402</v>
+        <v>2.13236021995544</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884706497192</v>
+        <v>2.18884682655334</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17825555801392</v>
+        <v>2.1782557964325</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584914207458</v>
+        <v>1.9858490228653</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230188846588</v>
+        <v>1.92230200767517</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637316703796</v>
+        <v>1.75637328624725</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991210460663</v>
+        <v>1.78991198539734</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08293509483337</v>
+        <v>2.08293461799622</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1535427570343</v>
+        <v>2.15354299545288</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351804733276</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177750587463</v>
+        <v>2.15177798271179</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001273155212</v>
+        <v>2.15001249313354</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706518173218</v>
+        <v>2.1270649433136</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542538642883</v>
+        <v>2.57542562484741</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723269462585</v>
+        <v>2.72723245620728</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192886352539</v>
+        <v>2.69192862510681</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.57423329353333</v>
+        <v>2.5742335319519</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789642333984</v>
+        <v>2.50789666175842</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841358184814</v>
+        <v>2.47841382026672</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G121" t="n">
-        <v>2.34205484390259</v>
+        <v>2.34205508232117</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544881820679</v>
+        <v>2.25544834136963</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252802848816</v>
+        <v>2.17252779006958</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228026390076</v>
+        <v>2.22228002548218</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G147" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102076530457</v>
+        <v>2.40102100372314</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G163" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>2.31441450119019</v>
+        <v>2.31441473960876</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097655296326</v>
+        <v>2.26097679138184</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517918586731</v>
+        <v>2.23517942428589</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G193" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731342315674</v>
+        <v>2.32731318473816</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338042259216</v>
+        <v>2.37338066101074</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785244941711</v>
+        <v>2.36785268783569</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915616035461</v>
+        <v>2.32915592193604</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G243" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G244" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G258" t="n">
-        <v>2.5650200843811</v>
+        <v>2.56501984596252</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G259" t="n">
-        <v>2.56317710876465</v>
+        <v>2.56317734718323</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477255821228</v>
+        <v>2.61477279663086</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715432167053</v>
+        <v>2.65715456008911</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.54659295082092</v>
+        <v>2.5465931892395</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845803260803</v>
+        <v>2.61845779418945</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>2.56686282157898</v>
+        <v>2.5668625831604</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G288" t="n">
-        <v>2.5576491355896</v>
+        <v>2.55764937400818</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061413764954</v>
+        <v>2.78061437606812</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349095344543</v>
+        <v>2.72349119186401</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>2.69032263755798</v>
+        <v>2.69032287597656</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G298" t="n">
-        <v>2.71059203147888</v>
+        <v>2.71059226989746</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169242858887</v>
+        <v>2.86169266700745</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616421699524</v>
+        <v>2.85616445541382</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G308" t="n">
-        <v>2.8174684047699</v>
+        <v>2.81746816635132</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036684989929</v>
+        <v>2.83036708831787</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.91513061523438</v>
+        <v>2.9151303768158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515272140503</v>
+        <v>2.98515248298645</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097243309021</v>
+        <v>3.08097219467163</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.26892638206482</v>
+        <v>3.2689266204834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.2707691192627</v>
+        <v>3.27076888084412</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993835449219</v>
+        <v>3.13993811607361</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937698364258</v>
+        <v>3.02937722206116</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470188140869</v>
+        <v>3.22470164299011</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414074897766</v>
+        <v>3.11414051055908</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099453926086</v>
+        <v>3.15099430084229</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441038131714</v>
+        <v>3.13441014289856</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151145935059</v>
+        <v>3.12151122093201</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045503616333</v>
+        <v>3.11045527458191</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0367476940155</v>
+        <v>3.03674793243408</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G353" t="n">
-        <v>2.98330998420715</v>
+        <v>2.98330974578857</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>3.04043292999268</v>
+        <v>3.04043316841125</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.26764059066772</v>
+        <v>3.2676408290863</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215288162231</v>
+        <v>3.29215264320374</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279123306274</v>
+        <v>3.18279147148132</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713451385498</v>
+        <v>3.17713475227356</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491203308105</v>
+        <v>3.11491179466248</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.92258667945862</v>
+        <v>2.9225869178772</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669505119324</v>
+        <v>2.98669528961182</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864684104919</v>
+        <v>2.88864707946777</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332766532898</v>
+        <v>2.94332790374756</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.82831001281738</v>
+        <v>2.8283097743988</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682804107666</v>
+        <v>2.78682827949524</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002689361572</v>
+        <v>2.80002665519714</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517777442932</v>
+        <v>2.71517753601074</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046635627747</v>
+        <v>2.99046611785889</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228539466858</v>
+        <v>3.09228563308716</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.07908654212952</v>
+        <v>3.0790867805481</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928590774536</v>
+        <v>2.77928566932678</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.4549732208252</v>
+        <v>2.45497298240662</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187628746033</v>
+        <v>2.57187652587891</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238212585449</v>
+        <v>2.66238236427307</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032817840576</v>
+        <v>2.63032793998718</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.50211143493652</v>
+        <v>2.5021116733551</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891258239746</v>
+        <v>2.48891282081604</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137044906616</v>
+        <v>2.48137068748474</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217781066895</v>
+        <v>2.40217804908752</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.524738073349</v>
+        <v>2.52473783493042</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399708747864</v>
+        <v>2.50399684906006</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834060668945</v>
+        <v>2.49834036827087</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005724906921</v>
+        <v>2.47005701065063</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520812988281</v>
+        <v>2.38520789146423</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.29093098640442</v>
+        <v>2.290931224823</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207589149475</v>
+        <v>2.27207565307617</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264786720276</v>
+        <v>2.26264810562134</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066005706787</v>
+        <v>2.13066029548645</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038924694061</v>
+        <v>1.97038900852203</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082611560822</v>
+        <v>1.88082599639893</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>0.344999998807907</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>3925</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.34400001168251</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125348091125</v>
+        <v>2.38125371932983</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652428627014</v>
+        <v>2.29652404785156</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419295310974</v>
+        <v>2.37419271469116</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771513938904</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34948015213013</v>
+        <v>2.34947991371155</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595796585083</v>
+        <v>2.37595820426941</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828953742981</v>
+        <v>2.29828929901123</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123708724976</v>
+        <v>2.32123684883118</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299378395081</v>
+        <v>2.29299354553223</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22415089607239</v>
+        <v>2.22415065765381</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062894821167</v>
+        <v>2.25062870979309</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181100845337</v>
+        <v>2.27181124687195</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475879669189</v>
+        <v>2.29475903511047</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236021995544</v>
+        <v>2.1323606967926</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412594795227</v>
+        <v>2.13412547111511</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230200767517</v>
+        <v>1.92230176925659</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637328624725</v>
+        <v>1.75637316703796</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08293461799622</v>
+        <v>2.08293485641479</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.15354299545288</v>
+        <v>2.1535427570343</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413426399231</v>
+        <v>2.16413402557373</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177798271179</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824748039246</v>
+        <v>2.14824724197388</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300233840942</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542562484741</v>
+        <v>2.57542538642883</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953052520752</v>
+        <v>2.52953028678894</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.59484267234802</v>
+        <v>2.5948429107666</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723245620728</v>
+        <v>2.72723269462585</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841382026672</v>
+        <v>2.47841358184814</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998668670654</v>
+        <v>2.45998692512512</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544834136963</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913381576538</v>
+        <v>2.25913405418396</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097679138184</v>
+        <v>2.26097655296326</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385336875916</v>
+        <v>2.20385313034058</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070715904236</v>
+        <v>2.24070692062378</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517942428589</v>
+        <v>2.23517918586731</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731318473816</v>
+        <v>2.32731366157532</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338066101074</v>
+        <v>2.37338042259216</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785268783569</v>
+        <v>2.36785244941711</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547044754028</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915592193604</v>
+        <v>2.32915616035461</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396389961243</v>
+        <v>2.55396413803101</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477279663086</v>
+        <v>2.61477255821228</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68848013877869</v>
+        <v>2.68847990036011</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5465931892395</v>
+        <v>2.54659295082092</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061437606812</v>
+        <v>2.78061413764954</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349119186401</v>
+        <v>2.72349143028259</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456924438477</v>
+        <v>2.80456900596619</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879374504089</v>
+        <v>2.84879350662231</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.9151303768158</v>
+        <v>2.91513061523438</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515248298645</v>
+        <v>2.98515272140503</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097219467163</v>
+        <v>3.08097243309021</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2689266204834</v>
+        <v>3.26892638206482</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993811607361</v>
+        <v>3.13993835449219</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461345672607</v>
+        <v>2.94461369514465</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.99068069458008</v>
+        <v>2.9906804561615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05886006355286</v>
+        <v>3.05885982513428</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470164299011</v>
+        <v>3.22470188140869</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099430084229</v>
+        <v>3.15099453926086</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441014289856</v>
+        <v>3.13441038131714</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>0.34400001168251</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>1473</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125371932983</v>
+        <v>2.38125348091125</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182787895203</v>
+        <v>2.33182811737061</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419271469116</v>
+        <v>2.37419295310974</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181124687195</v>
+        <v>2.27181100845337</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475879669189</v>
+        <v>2.29475855827332</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412547111511</v>
+        <v>2.13412594795227</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584926128387</v>
+        <v>1.9858490228653</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347599029541</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7793208360672</v>
+        <v>1.77932095527649</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637316703796</v>
+        <v>1.75637304782867</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1535427570343</v>
+        <v>2.15354299545288</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351757049561</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413426399231</v>
+        <v>2.16413402557373</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.10058689117432</v>
+        <v>2.1005871295929</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648199081421</v>
+        <v>2.14648222923279</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296004295349</v>
+        <v>2.17296028137207</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360144615173</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360144615173</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534151077271</v>
+        <v>2.27534174919128</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481796264648</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542538642883</v>
+        <v>2.57542562484741</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.5948429107666</v>
+        <v>2.59484243392944</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664190292358</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664190292358</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369450569153</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.57423329353333</v>
+        <v>2.5742335319519</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605392456055</v>
+        <v>2.50605416297913</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841358184814</v>
+        <v>2.47841382026672</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998692512512</v>
+        <v>2.45998668670654</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099865913391</v>
+        <v>2.33099889755249</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753884315491</v>
+        <v>2.20753860473633</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544857978821</v>
+        <v>2.25544834136963</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913405418396</v>
+        <v>2.25913381576538</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228026390076</v>
+        <v>2.22228002548218</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.43418908119202</v>
+        <v>2.4341893196106</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099865913391</v>
+        <v>2.33099889755249</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097655296326</v>
+        <v>2.26097679138184</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385313034058</v>
+        <v>2.20385336875916</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.2480776309967</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070692062378</v>
+        <v>2.24070715904236</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517918586731</v>
+        <v>2.23517942428589</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731366157532</v>
+        <v>2.32731318473816</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391944885254</v>
+        <v>2.41391968727112</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338042259216</v>
+        <v>2.37338066101074</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785244941711</v>
+        <v>2.36785268783569</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549279212952</v>
+        <v>2.39549255371094</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547044754028</v>
+        <v>2.32547068595886</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965121269226</v>
+        <v>2.22965097427368</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915616035461</v>
+        <v>2.32915592193604</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391944885254</v>
+        <v>2.41391968727112</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396413803101</v>
+        <v>2.55396389961243</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477255821228</v>
+        <v>2.61477279663086</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76402997970581</v>
+        <v>2.76403021812439</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715432167053</v>
+        <v>2.65715456008911</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68847990036011</v>
+        <v>2.68848013877869</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.6442551612854</v>
+        <v>2.64425539970398</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976126670837</v>
+        <v>2.57976150512695</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.54659295082092</v>
+        <v>2.5465931892395</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845803260803</v>
+        <v>2.61845779418945</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657108306885</v>
+        <v>2.47657084465027</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369450569153</v>
+        <v>2.53369426727295</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061413764954</v>
+        <v>2.78061437606812</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349143028259</v>
+        <v>2.72349119186401</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76402997970581</v>
+        <v>2.76403021812439</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169242858887</v>
+        <v>2.86169266700745</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036684989929</v>
+        <v>2.83036708831787</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456900596619</v>
+        <v>2.80456924438477</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879350662231</v>
+        <v>2.84879374504089</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.91513061523438</v>
+        <v>2.9151303768158</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515272140503</v>
+        <v>2.98515248298645</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780411720276</v>
+        <v>3.04780387878418</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097243309021</v>
+        <v>3.08097219467163</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.26892638206482</v>
+        <v>3.2689266204834</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993835449219</v>
+        <v>3.13993811607361</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.0072648525238</v>
+        <v>3.00726461410522</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461369514465</v>
+        <v>2.94461345672607</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.9906804561615</v>
+        <v>2.99068069458008</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964661598206</v>
+        <v>3.04964637756348</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05885982513428</v>
+        <v>3.05886006355286</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470188140869</v>
+        <v>3.22470164299011</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414074897766</v>
+        <v>3.11414051055908</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099453926086</v>
+        <v>3.15099430084229</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441038131714</v>
+        <v>3.13441014289856</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151145935059</v>
+        <v>3.12151122093201</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>0.328000009059906</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>7311</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -63254,6 +63254,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="F2735" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>4540</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.323000013828278</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.333999991416931</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.323000013828278</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.323000013828278</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.314999997615814</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.314999997615814</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>0.314999997615814</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.330000013113022</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478398323059</v>
+        <v>2.38478422164917</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419319152832</v>
+        <v>2.37419271469116</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771490097046</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34947991371155</v>
+        <v>2.34948015213013</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828929901123</v>
+        <v>2.29828953742981</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299354553223</v>
+        <v>2.29299378395081</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003791809082</v>
+        <v>2.24003767967224</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347575187683</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230176925659</v>
+        <v>1.92230188846588</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7793208360672</v>
+        <v>1.77932071685791</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637304782867</v>
+        <v>1.75637316703796</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351804733276</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177798271179</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824724197388</v>
+        <v>2.14824748039246</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.1270649433136</v>
+        <v>2.12706518173218</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530800819397</v>
+        <v>2.15530824661255</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648222923279</v>
+        <v>2.14648199081421</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828098297119</v>
+        <v>2.26828074455261</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300186157227</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481748580933</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542562484741</v>
+        <v>2.57542538642883</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953028678894</v>
+        <v>2.52953052520752</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723245620728</v>
+        <v>2.72723269462585</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G84" t="n">
-        <v>2.67604207992554</v>
+        <v>2.67604184150696</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841382026672</v>
+        <v>2.47841358184814</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998668670654</v>
+        <v>2.45998692512512</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544834136963</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913381576538</v>
+        <v>2.25913405418396</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097679138184</v>
+        <v>2.26097655296326</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385336875916</v>
+        <v>2.20385313034058</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070715904236</v>
+        <v>2.24070692062378</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517942428589</v>
+        <v>2.23517918586731</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731318473816</v>
+        <v>2.32731366157532</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338066101074</v>
+        <v>2.37338042259216</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785268783569</v>
+        <v>2.36785244941711</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547044754028</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915592193604</v>
+        <v>2.32915616035461</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396389961243</v>
+        <v>2.55396413803101</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477279663086</v>
+        <v>2.61477255821228</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68848013877869</v>
+        <v>2.68847990036011</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5465931892395</v>
+        <v>2.54659295082092</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061437606812</v>
+        <v>2.78061413764954</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349119186401</v>
+        <v>2.72349143028259</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456924438477</v>
+        <v>2.80456900596619</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879374504089</v>
+        <v>2.84879350662231</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.9151303768158</v>
+        <v>2.91513061523438</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515248298645</v>
+        <v>2.98515272140503</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097219467163</v>
+        <v>3.08097243309021</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2689266204834</v>
+        <v>3.26892638206482</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993811607361</v>
+        <v>3.13993835449219</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461345672607</v>
+        <v>2.94461369514465</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.99068069458008</v>
+        <v>2.9906804561615</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05886006355286</v>
+        <v>3.05885982513428</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470164299011</v>
+        <v>3.22470188140869</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099430084229</v>
+        <v>3.15099453926086</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441014289856</v>
+        <v>3.13441038131714</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.340999990701675</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>17633</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.321000009775162</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771490097046</v>
+        <v>2.34771466255188</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595772743225</v>
+        <v>2.37595796585083</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -688,7 +688,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828929901123</v>
+        <v>2.29828953742981</v>
       </c>
       <c r="H11" t="n">
         <v>26500</v>
@@ -717,7 +717,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123708724976</v>
+        <v>2.32123684883118</v>
       </c>
       <c r="H12" t="n">
         <v>24500</v>
@@ -746,7 +746,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299402236938</v>
+        <v>2.29299378395081</v>
       </c>
       <c r="H13" t="n">
         <v>49000</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181124687195</v>
+        <v>2.27181100845337</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003791809082</v>
+        <v>2.24003767967224</v>
       </c>
       <c r="H17" t="n">
         <v>35500</v>
@@ -891,7 +891,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28063750267029</v>
+        <v>2.28063726425171</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884706497192</v>
+        <v>2.18884682655334</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1007,7 +1007,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120310783386</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17825555801392</v>
+        <v>2.1782557964325</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1065,7 +1065,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412594795227</v>
+        <v>2.13412570953369</v>
       </c>
       <c r="H24" t="n">
         <v>17000</v>
@@ -1152,7 +1152,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584890365601</v>
+        <v>1.98584914207458</v>
       </c>
       <c r="H27" t="n">
         <v>30500</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347587108612</v>
+        <v>1.91347563266754</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1210,7 +1210,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230176925659</v>
+        <v>1.92230188846588</v>
       </c>
       <c r="H29" t="n">
         <v>53000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990343093872</v>
+        <v>1.7599036693573</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991198539734</v>
+        <v>1.78991210460663</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1355,7 +1355,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H34" t="n">
         <v>70500</v>
@@ -1442,7 +1442,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120310783386</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1587,7 +1587,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H42" t="n">
         <v>6500</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H50" t="n">
         <v>11500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177750587463</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2196,7 +2196,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H63" t="n">
         <v>46500</v>
@@ -2225,7 +2225,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300233840942</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709012985229</v>
+        <v>2.21709036827087</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534198760986</v>
+        <v>2.27534174919128</v>
       </c>
       <c r="H69" t="n">
         <v>6500</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297691345215</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481748580933</v>
+        <v>2.50481772422791</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2573,7 +2573,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953052520752</v>
+        <v>2.52953028678894</v>
       </c>
       <c r="H76" t="n">
         <v>98500</v>
@@ -2631,7 +2631,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.61249446868896</v>
+        <v>2.61249470710754</v>
       </c>
       <c r="H78" t="n">
         <v>55000</v>
@@ -2747,7 +2747,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192862510681</v>
+        <v>2.69192886352539</v>
       </c>
       <c r="H82" t="n">
         <v>91000</v>
@@ -2776,7 +2776,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.70958065986633</v>
+        <v>2.70958042144775</v>
       </c>
       <c r="H83" t="n">
         <v>24000</v>
@@ -2863,7 +2863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H86" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H88" t="n">
         <v>42500</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H99" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.57423329353333</v>
+        <v>2.5742335319519</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3327,7 +3327,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G102" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789642333984</v>
+        <v>2.50789666175842</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G109" t="n">
-        <v>2.47104287147522</v>
+        <v>2.47104263305664</v>
       </c>
       <c r="H109" t="n">
         <v>3500</v>
@@ -3559,7 +3559,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841358184814</v>
+        <v>2.47841382026672</v>
       </c>
       <c r="H110" t="n">
         <v>3000</v>
@@ -3878,7 +3878,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G121" t="n">
-        <v>2.34205484390259</v>
+        <v>2.34205508232117</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544881820679</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252802848816</v>
+        <v>2.17252779006958</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228026390076</v>
+        <v>2.22228002548218</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G151" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H151" t="n">
         <v>23000</v>
@@ -4777,7 +4777,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H152" t="n">
         <v>13000</v>
@@ -4864,7 +4864,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="n">
         <v>4500</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -4922,7 +4922,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G157" t="n">
-        <v>2.31625723838806</v>
+        <v>2.31625699996948</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>2.31441450119019</v>
+        <v>2.31441473960876</v>
       </c>
       <c r="H164" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5299,7 +5299,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>2.29783034324646</v>
+        <v>2.29783010482788</v>
       </c>
       <c r="H170" t="n">
         <v>1500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H200" t="n">
         <v>6500</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6778,7 +6778,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338042259216</v>
+        <v>2.37338066101074</v>
       </c>
       <c r="H221" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7126,7 +7126,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547092437744</v>
       </c>
       <c r="H233" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.2296507358551</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7764,7 +7764,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H255" t="n">
         <v>19500</v>
@@ -7880,7 +7880,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G259" t="n">
-        <v>2.56317710876465</v>
+        <v>2.56317734718323</v>
       </c>
       <c r="H259" t="n">
         <v>20000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715432167053</v>
+        <v>2.65715456008911</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8431,7 +8431,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H278" t="n">
         <v>6500</v>
@@ -8518,7 +8518,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G281" t="n">
-        <v>2.65899682044983</v>
+        <v>2.65899705886841</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845803260803</v>
+        <v>2.61845779418945</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H289" t="n">
         <v>59000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G304" t="n">
-        <v>2.89117550849915</v>
+        <v>2.89117574691772</v>
       </c>
       <c r="H304" t="n">
         <v>56500</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169242858887</v>
+        <v>2.86169266700745</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616421699524</v>
+        <v>2.85616445541382</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9301,7 +9301,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G308" t="n">
-        <v>2.8174684047699</v>
+        <v>2.81746816635132</v>
       </c>
       <c r="H308" t="n">
         <v>9000</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G313" t="n">
-        <v>2.88749027252197</v>
+        <v>2.88749003410339</v>
       </c>
       <c r="H313" t="n">
         <v>30500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036684989929</v>
+        <v>2.83036708831787</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9533,7 +9533,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G316" t="n">
-        <v>2.88749027252197</v>
+        <v>2.88749003410339</v>
       </c>
       <c r="H316" t="n">
         <v>34500</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.2707691192627</v>
+        <v>3.27076888084412</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9852,7 +9852,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G327" t="n">
-        <v>3.15652251243591</v>
+        <v>3.15652275085449</v>
       </c>
       <c r="H327" t="n">
         <v>64500</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10200,7 +10200,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15836501121521</v>
+        <v>3.15836524963379</v>
       </c>
       <c r="H339" t="n">
         <v>19000</v>
@@ -10287,7 +10287,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G342" t="n">
-        <v>3.22654461860657</v>
+        <v>3.22654485702515</v>
       </c>
       <c r="H342" t="n">
         <v>10500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414074897766</v>
+        <v>3.11414051055908</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10461,7 +10461,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099453926086</v>
+        <v>3.15099430084229</v>
       </c>
       <c r="H348" t="n">
         <v>9500</v>
@@ -10490,7 +10490,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441038131714</v>
+        <v>3.13441014289856</v>
       </c>
       <c r="H349" t="n">
         <v>16000</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151145935059</v>
+        <v>3.12151122093201</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045503616333</v>
+        <v>3.11045527458191</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10635,7 +10635,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>3.04043292999268</v>
+        <v>3.04043316841125</v>
       </c>
       <c r="H354" t="n">
         <v>15000</v>
@@ -79951,6 +79951,64 @@
         <v>0</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>110</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.335999995470047</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478398323059</v>
+        <v>2.38478422164917</v>
       </c>
       <c r="H2" t="n">
         <v>35500</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182787895203</v>
+        <v>2.33182811737061</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771513938904</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -630,7 +630,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34948015213013</v>
+        <v>2.34947991371155</v>
       </c>
       <c r="H9" t="n">
         <v>4500</v>
@@ -804,7 +804,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062894821167</v>
+        <v>2.25062870979309</v>
       </c>
       <c r="H15" t="n">
         <v>27500</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181100845337</v>
+        <v>2.27181124687195</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003767967224</v>
+        <v>2.2400381565094</v>
       </c>
       <c r="H17" t="n">
         <v>35500</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884682655334</v>
+        <v>2.18884706497192</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1007,7 +1007,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120310783386</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1782557964325</v>
+        <v>2.17825555801392</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1123,7 +1123,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1152,7 +1152,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584914207458</v>
+        <v>1.9858490228653</v>
       </c>
       <c r="H27" t="n">
         <v>30500</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347563266754</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1210,7 +1210,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230188846588</v>
+        <v>1.9223016500473</v>
       </c>
       <c r="H29" t="n">
         <v>53000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7599036693573</v>
+        <v>1.75990343093872</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991210460663</v>
+        <v>1.78991198539734</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1355,7 +1355,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H34" t="n">
         <v>70500</v>
@@ -1384,7 +1384,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H35" t="n">
         <v>74000</v>
@@ -1413,7 +1413,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G36" t="n">
-        <v>2.08293509483337</v>
+        <v>2.08293485641479</v>
       </c>
       <c r="H36" t="n">
         <v>24000</v>
@@ -1442,7 +1442,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120310783386</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1500,7 +1500,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H39" t="n">
         <v>23000</v>
@@ -1529,7 +1529,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351804733276</v>
       </c>
       <c r="H41" t="n">
         <v>9500</v>
@@ -1587,7 +1587,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H42" t="n">
         <v>6500</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1674,7 +1674,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413402557373</v>
+        <v>2.16413378715515</v>
       </c>
       <c r="H45" t="n">
         <v>32500</v>
@@ -1761,7 +1761,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H48" t="n">
         <v>45500</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H50" t="n">
         <v>11500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648222923279</v>
+        <v>2.14648199081421</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="n">
         <v>12000</v>
@@ -2196,7 +2196,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H63" t="n">
         <v>46500</v>
@@ -2225,7 +2225,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300233840942</v>
+        <v>2.32300186157227</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709036827087</v>
+        <v>2.21709012985229</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481748580933</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2631,7 +2631,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.61249470710754</v>
+        <v>2.61249446868896</v>
       </c>
       <c r="H78" t="n">
         <v>55000</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2747,7 +2747,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192886352539</v>
+        <v>2.69192838668823</v>
       </c>
       <c r="H82" t="n">
         <v>91000</v>
@@ -2805,7 +2805,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G84" t="n">
-        <v>2.67604207992554</v>
+        <v>2.67604184150696</v>
       </c>
       <c r="H84" t="n">
         <v>32500</v>
@@ -2950,7 +2950,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3066,7 +3066,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="n">
         <v>5500</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3327,7 +3327,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789666175842</v>
+        <v>2.50789642333984</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3414,7 +3414,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="n">
         <v>15500</v>
@@ -3530,7 +3530,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G109" t="n">
-        <v>2.47104263305664</v>
+        <v>2.47104287147522</v>
       </c>
       <c r="H109" t="n">
         <v>3500</v>
@@ -3588,7 +3588,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H111" t="n">
         <v>3000</v>
@@ -3617,7 +3617,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4255,7 +4255,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252779006958</v>
+        <v>2.17252802848816</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G147" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H147" t="n">
         <v>10500</v>
@@ -4690,7 +4690,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="n">
         <v>16000</v>
@@ -4719,7 +4719,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="n">
         <v>1000</v>
@@ -4748,7 +4748,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G151" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H151" t="n">
         <v>23000</v>
@@ -4835,7 +4835,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H154" t="n">
         <v>2500</v>
@@ -4864,7 +4864,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.43418908119202</v>
+        <v>2.4341893196106</v>
       </c>
       <c r="H155" t="n">
         <v>4500</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -4922,7 +4922,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G157" t="n">
-        <v>2.31625699996948</v>
+        <v>2.31625723838806</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -5096,7 +5096,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G163" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H163" t="n">
         <v>9000</v>
@@ -5299,7 +5299,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>2.29783010482788</v>
+        <v>2.29783034324646</v>
       </c>
       <c r="H170" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H172" t="n">
         <v>21000</v>
@@ -5386,7 +5386,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H173" t="n">
         <v>11000</v>
@@ -5415,7 +5415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5589,7 +5589,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H180" t="n">
         <v>43000</v>
@@ -5966,7 +5966,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G193" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H193" t="n">
         <v>35500</v>
@@ -5995,7 +5995,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H194" t="n">
         <v>7500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6082,7 +6082,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="n">
         <v>65000</v>
@@ -6111,7 +6111,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H198" t="n">
         <v>20000</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758305549622</v>
+        <v>2.34758281707764</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890863418579</v>
+        <v>2.37890887260437</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6546,7 +6546,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H213" t="n">
         <v>8000</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="n">
         <v>8500</v>
@@ -7039,7 +7039,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7126,7 +7126,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547092437744</v>
+        <v>2.32547068595886</v>
       </c>
       <c r="H233" t="n">
         <v>4500</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.2296507358551</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7387,7 +7387,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H242" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G243" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7445,7 +7445,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G244" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7851,7 +7851,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G258" t="n">
-        <v>2.5650200843811</v>
+        <v>2.56501984596252</v>
       </c>
       <c r="H258" t="n">
         <v>35000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663716316223</v>
+        <v>2.68663692474365</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8286,7 +8286,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="n">
         <v>13000</v>
@@ -8460,7 +8460,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.54659295082092</v>
+        <v>2.5465931892395</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G281" t="n">
-        <v>2.65899705886841</v>
+        <v>2.65899682044983</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8605,7 +8605,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>2.56686282157898</v>
+        <v>2.5668625831604</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="n">
         <v>8500</v>
@@ -8692,7 +8692,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G288" t="n">
-        <v>2.5576491355896</v>
+        <v>2.55764937400818</v>
       </c>
       <c r="H288" t="n">
         <v>3500</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8924,7 +8924,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349095344543</v>
+        <v>2.72349119186401</v>
       </c>
       <c r="H295" t="n">
         <v>13500</v>
@@ -8982,7 +8982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>2.69032263755798</v>
+        <v>2.69032287597656</v>
       </c>
       <c r="H297" t="n">
         <v>33000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G298" t="n">
-        <v>2.71059203147888</v>
+        <v>2.71059226989746</v>
       </c>
       <c r="H298" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G304" t="n">
-        <v>2.89117574691772</v>
+        <v>2.89117550849915</v>
       </c>
       <c r="H304" t="n">
         <v>56500</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616445541382</v>
+        <v>2.85616421699524</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088376998901</v>
+        <v>2.80088400840759</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G313" t="n">
-        <v>2.88749003410339</v>
+        <v>2.88749027252197</v>
       </c>
       <c r="H313" t="n">
         <v>30500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9533,7 +9533,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G316" t="n">
-        <v>2.88749003410339</v>
+        <v>2.88749027252197</v>
       </c>
       <c r="H316" t="n">
         <v>34500</v>
@@ -9649,7 +9649,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="n">
         <v>33500</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202837944031</v>
+        <v>3.09202861785889</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.27076888084412</v>
+        <v>3.2707691192627</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9852,7 +9852,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G327" t="n">
-        <v>3.15652275085449</v>
+        <v>3.15652251243591</v>
       </c>
       <c r="H327" t="n">
         <v>64500</v>
@@ -9968,7 +9968,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10084,7 +10084,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="n">
         <v>9500</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10200,7 +10200,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15836524963379</v>
+        <v>3.15836501121521</v>
       </c>
       <c r="H339" t="n">
         <v>19000</v>
@@ -10287,7 +10287,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G342" t="n">
-        <v>3.22654485702515</v>
+        <v>3.22654461860657</v>
       </c>
       <c r="H342" t="n">
         <v>10500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045527458191</v>
+        <v>3.11045503616333</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10606,7 +10606,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G353" t="n">
-        <v>2.98330998420715</v>
+        <v>2.98330974578857</v>
       </c>
       <c r="H353" t="n">
         <v>23000</v>
@@ -80009,6 +80009,35 @@
         <v>2600</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.337999999523163</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>6697</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652404785156</v>
+        <v>2.29652428627014</v>
       </c>
       <c r="H5" t="n">
         <v>20500</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771513938904</v>
+        <v>2.34771466255188</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -630,7 +630,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34947991371155</v>
+        <v>2.34948015213013</v>
       </c>
       <c r="H9" t="n">
         <v>4500</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595796585083</v>
+        <v>2.37595820426941</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -804,7 +804,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062870979309</v>
+        <v>2.25062894821167</v>
       </c>
       <c r="H15" t="n">
         <v>27500</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181124687195</v>
+        <v>2.27181100845337</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2400381565094</v>
+        <v>2.24003791809082</v>
       </c>
       <c r="H17" t="n">
         <v>35500</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884706497192</v>
+        <v>2.18884682655334</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1007,7 +1007,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120310783386</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17825555801392</v>
+        <v>2.1782557964325</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1123,7 +1123,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347587108612</v>
+        <v>1.91347563266754</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1210,7 +1210,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.9223016500473</v>
+        <v>1.92230200767517</v>
       </c>
       <c r="H29" t="n">
         <v>53000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990343093872</v>
+        <v>1.75990355014801</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991198539734</v>
+        <v>1.78991210460663</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1355,7 +1355,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H34" t="n">
         <v>70500</v>
@@ -1384,7 +1384,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H35" t="n">
         <v>74000</v>
@@ -1442,7 +1442,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120310783386</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1500,7 +1500,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H39" t="n">
         <v>23000</v>
@@ -1529,7 +1529,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H42" t="n">
         <v>6500</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1674,7 +1674,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413378715515</v>
+        <v>2.16413426399231</v>
       </c>
       <c r="H45" t="n">
         <v>32500</v>
@@ -1761,7 +1761,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H48" t="n">
         <v>45500</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H50" t="n">
         <v>11500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177774429321</v>
+        <v>2.15177798271179</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -1935,7 +1935,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.12000393867493</v>
+        <v>2.12000417709351</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001273155212</v>
+        <v>2.15001249313354</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706518173218</v>
+        <v>2.1270649433136</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530800819397</v>
+        <v>2.15530824661255</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648199081421</v>
+        <v>2.14648222923279</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296004295349</v>
+        <v>2.17296028137207</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828098297119</v>
+        <v>2.26828074455261</v>
       </c>
       <c r="H62" t="n">
         <v>12000</v>
@@ -2196,7 +2196,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H63" t="n">
         <v>46500</v>
@@ -2225,7 +2225,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360168457031</v>
+        <v>2.36360192298889</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300186157227</v>
+        <v>2.32300233840942</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709012985229</v>
+        <v>2.21709036827087</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481748580933</v>
+        <v>2.50481772422791</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2573,7 +2573,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953028678894</v>
+        <v>2.52953052520752</v>
       </c>
       <c r="H76" t="n">
         <v>98500</v>
@@ -2631,7 +2631,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.61249446868896</v>
+        <v>2.61249470710754</v>
       </c>
       <c r="H78" t="n">
         <v>55000</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723269462585</v>
+        <v>2.72723245620728</v>
       </c>
       <c r="H81" t="n">
         <v>19500</v>
@@ -2747,7 +2747,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192838668823</v>
+        <v>2.69192862510681</v>
       </c>
       <c r="H82" t="n">
         <v>91000</v>
@@ -2805,7 +2805,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G84" t="n">
-        <v>2.67604184150696</v>
+        <v>2.67604207992554</v>
       </c>
       <c r="H84" t="n">
         <v>32500</v>
@@ -2950,7 +2950,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3066,7 +3066,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H93" t="n">
         <v>5500</v>
@@ -3095,7 +3095,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.57423329353333</v>
+        <v>2.5742335319519</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789642333984</v>
+        <v>2.50789666175842</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3414,7 +3414,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605392456055</v>
+        <v>2.50605416297913</v>
       </c>
       <c r="H105" t="n">
         <v>15500</v>
@@ -3443,7 +3443,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H106" t="n">
         <v>14000</v>
@@ -3472,7 +3472,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -3733,7 +3733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H116" t="n">
         <v>27000</v>
@@ -3791,7 +3791,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H118" t="n">
         <v>21500</v>
@@ -3907,7 +3907,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H123" t="n">
         <v>1500</v>
@@ -3965,7 +3965,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H124" t="n">
         <v>13500</v>
@@ -3994,7 +3994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H125" t="n">
         <v>44000</v>
@@ -4023,7 +4023,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H126" t="n">
         <v>38000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4139,7 +4139,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H130" t="n">
         <v>22500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4255,7 +4255,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753884315491</v>
+        <v>2.20753860473633</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544857978821</v>
+        <v>2.25544834136963</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252802848816</v>
+        <v>2.17252779006958</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4487,7 +4487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H142" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228026390076</v>
+        <v>2.22228002548218</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H149" t="n">
         <v>16000</v>
@@ -4719,7 +4719,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H150" t="n">
         <v>1000</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -5009,7 +5009,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102076530457</v>
+        <v>2.40102100372314</v>
       </c>
       <c r="H160" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5473,7 +5473,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097655296326</v>
+        <v>2.26097679138184</v>
       </c>
       <c r="H178" t="n">
         <v>73000</v>
@@ -5676,7 +5676,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H184" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H185" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517918586731</v>
+        <v>2.23517942428589</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5937,7 +5937,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H192" t="n">
         <v>11500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H196" t="n">
         <v>17000</v>
@@ -6082,7 +6082,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H197" t="n">
         <v>65000</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758281707764</v>
+        <v>2.34758305549622</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6372,7 +6372,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731342315674</v>
+        <v>2.32731318473816</v>
       </c>
       <c r="H207" t="n">
         <v>14000</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890887260437</v>
+        <v>2.37890863418579</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6488,7 +6488,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H211" t="n">
         <v>47500</v>
@@ -6517,7 +6517,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H212" t="n">
         <v>12500</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6836,7 +6836,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H223" t="n">
         <v>500</v>
@@ -6865,7 +6865,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H224" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H227" t="n">
         <v>8500</v>
@@ -6981,7 +6981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785244941711</v>
+        <v>2.36785268783569</v>
       </c>
       <c r="H228" t="n">
         <v>4500</v>
@@ -7039,7 +7039,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965121269226</v>
+        <v>2.22965097427368</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7358,7 +7358,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915616035461</v>
+        <v>2.32915592193604</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7822,7 +7822,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H257" t="n">
         <v>21000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8025,7 +8025,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477255821228</v>
+        <v>2.61477279663086</v>
       </c>
       <c r="H264" t="n">
         <v>20000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715432167053</v>
+        <v>2.65715456008911</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663692474365</v>
+        <v>2.68663716316223</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8286,7 +8286,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.6442551612854</v>
+        <v>2.64425539970398</v>
       </c>
       <c r="H273" t="n">
         <v>13000</v>
@@ -8402,7 +8402,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H277" t="n">
         <v>13000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845803260803</v>
+        <v>2.61845779418945</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8634,7 +8634,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657108306885</v>
+        <v>2.47657084465027</v>
       </c>
       <c r="H285" t="n">
         <v>8500</v>
@@ -8692,7 +8692,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H287" t="n">
         <v>5000</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8895,7 +8895,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061413764954</v>
+        <v>2.78061437606812</v>
       </c>
       <c r="H294" t="n">
         <v>29000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169242858887</v>
+        <v>2.86169266700745</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616421699524</v>
+        <v>2.85616445541382</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088400840759</v>
+        <v>2.80088376998901</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036684989929</v>
+        <v>2.83036708831787</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9591,7 +9591,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.91513061523438</v>
+        <v>2.9151303768158</v>
       </c>
       <c r="H318" t="n">
         <v>29000</v>
@@ -9620,7 +9620,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515272140503</v>
+        <v>2.98515248298645</v>
       </c>
       <c r="H319" t="n">
         <v>51500</v>
@@ -9649,7 +9649,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780411720276</v>
+        <v>3.04780387878418</v>
       </c>
       <c r="H320" t="n">
         <v>33500</v>
@@ -9678,7 +9678,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097243309021</v>
+        <v>3.08097219467163</v>
       </c>
       <c r="H321" t="n">
         <v>110500</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202861785889</v>
+        <v>3.09202837944031</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9765,7 +9765,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.26892638206482</v>
+        <v>3.2689266204834</v>
       </c>
       <c r="H324" t="n">
         <v>81500</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.2707691192627</v>
+        <v>3.27076888084412</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9910,7 +9910,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993835449219</v>
+        <v>3.13993811607361</v>
       </c>
       <c r="H329" t="n">
         <v>22000</v>
@@ -9939,7 +9939,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937698364258</v>
+        <v>3.02937722206116</v>
       </c>
       <c r="H330" t="n">
         <v>27500</v>
@@ -9968,7 +9968,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.0072648525238</v>
+        <v>3.00726461410522</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10084,7 +10084,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964661598206</v>
+        <v>3.04964637756348</v>
       </c>
       <c r="H335" t="n">
         <v>9500</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10258,7 +10258,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470188140869</v>
+        <v>3.22470164299011</v>
       </c>
       <c r="H341" t="n">
         <v>21500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414074897766</v>
+        <v>3.11414051055908</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151145935059</v>
+        <v>3.12151122093201</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045503616333</v>
+        <v>3.11045527458191</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10577,7 +10577,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0367476940155</v>
+        <v>3.03674793243408</v>
       </c>
       <c r="H352" t="n">
         <v>22000</v>
@@ -10693,7 +10693,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.26764059066772</v>
+        <v>3.2676408290863</v>
       </c>
       <c r="H356" t="n">
         <v>94000</v>
@@ -10838,7 +10838,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215288162231</v>
+        <v>3.29215264320374</v>
       </c>
       <c r="H361" t="n">
         <v>33000</v>
@@ -10867,7 +10867,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279123306274</v>
+        <v>3.18279147148132</v>
       </c>
       <c r="H362" t="n">
         <v>64000</v>
@@ -10954,7 +10954,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713451385498</v>
+        <v>3.17713475227356</v>
       </c>
       <c r="H365" t="n">
         <v>20500</v>
@@ -10983,7 +10983,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491203308105</v>
+        <v>3.11491179466248</v>
       </c>
       <c r="H366" t="n">
         <v>14500</v>
@@ -11302,7 +11302,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H377" t="n">
         <v>25500</v>
@@ -11447,7 +11447,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H382" t="n">
         <v>10500</v>
@@ -11563,7 +11563,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.92258667945862</v>
+        <v>2.9225869178772</v>
       </c>
       <c r="H386" t="n">
         <v>6000</v>
@@ -11592,7 +11592,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H389" t="n">
         <v>16000</v>
@@ -11708,7 +11708,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669505119324</v>
+        <v>2.98669528961182</v>
       </c>
       <c r="H391" t="n">
         <v>16000</v>
@@ -11824,7 +11824,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864684104919</v>
+        <v>2.88864707946777</v>
       </c>
       <c r="H395" t="n">
         <v>6500</v>
@@ -11853,7 +11853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H396" t="n">
         <v>6500</v>
@@ -11911,7 +11911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H399" t="n">
         <v>5000</v>
@@ -11969,7 +11969,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332766532898</v>
+        <v>2.94332790374756</v>
       </c>
       <c r="H400" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H406" t="n">
         <v>18000</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.82831001281738</v>
+        <v>2.8283097743988</v>
       </c>
       <c r="H409" t="n">
         <v>8500</v>
@@ -12346,7 +12346,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682804107666</v>
+        <v>2.78682827949524</v>
       </c>
       <c r="H413" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002689361572</v>
+        <v>2.80002665519714</v>
       </c>
       <c r="H414" t="n">
         <v>7000</v>
@@ -12462,7 +12462,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H417" t="n">
         <v>5500</v>
@@ -12694,7 +12694,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517777442932</v>
+        <v>2.71517753601074</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12752,7 +12752,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046635627747</v>
+        <v>2.99046611785889</v>
       </c>
       <c r="H427" t="n">
         <v>411000</v>
@@ -12839,7 +12839,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H430" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H434" t="n">
         <v>36000</v>
@@ -12984,7 +12984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H435" t="n">
         <v>18000</v>
@@ -13013,7 +13013,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H436" t="n">
         <v>2500</v>
@@ -13100,7 +13100,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H439" t="n">
         <v>82500</v>
@@ -13245,7 +13245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228539466858</v>
+        <v>3.09228563308716</v>
       </c>
       <c r="H444" t="n">
         <v>47000</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.07908654212952</v>
+        <v>3.0790867805481</v>
       </c>
       <c r="H446" t="n">
         <v>25500</v>
@@ -13390,7 +13390,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928590774536</v>
+        <v>2.77928566932678</v>
       </c>
       <c r="H449" t="n">
         <v>531500</v>
@@ -13506,7 +13506,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.4549732208252</v>
+        <v>2.45497298240662</v>
       </c>
       <c r="H453" t="n">
         <v>144500</v>
@@ -13535,7 +13535,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H454" t="n">
         <v>47000</v>
@@ -13593,7 +13593,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H456" t="n">
         <v>146500</v>
@@ -13680,7 +13680,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187628746033</v>
+        <v>2.57187652587891</v>
       </c>
       <c r="H459" t="n">
         <v>26500</v>
@@ -13738,7 +13738,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238212585449</v>
+        <v>2.66238236427307</v>
       </c>
       <c r="H461" t="n">
         <v>152500</v>
@@ -13767,7 +13767,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H462" t="n">
         <v>60000</v>
@@ -13825,7 +13825,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032817840576</v>
+        <v>2.63032793998718</v>
       </c>
       <c r="H464" t="n">
         <v>17500</v>
@@ -14173,7 +14173,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.50211143493652</v>
+        <v>2.5021116733551</v>
       </c>
       <c r="H476" t="n">
         <v>49500</v>
@@ -14202,7 +14202,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891258239746</v>
+        <v>2.48891282081604</v>
       </c>
       <c r="H477" t="n">
         <v>26500</v>
@@ -14231,7 +14231,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137044906616</v>
+        <v>2.48137068748474</v>
       </c>
       <c r="H478" t="n">
         <v>74500</v>
@@ -14289,7 +14289,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H480" t="n">
         <v>32000</v>
@@ -14492,7 +14492,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217781066895</v>
+        <v>2.40217804908752</v>
       </c>
       <c r="H487" t="n">
         <v>20000</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.524738073349</v>
+        <v>2.52473783493042</v>
       </c>
       <c r="H494" t="n">
         <v>26000</v>
@@ -14724,7 +14724,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399708747864</v>
+        <v>2.50399684906006</v>
       </c>
       <c r="H495" t="n">
         <v>14500</v>
@@ -14811,7 +14811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834060668945</v>
+        <v>2.49834036827087</v>
       </c>
       <c r="H498" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005724906921</v>
+        <v>2.47005701065063</v>
       </c>
       <c r="H499" t="n">
         <v>36500</v>
@@ -14898,7 +14898,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H501" t="n">
         <v>14500</v>
@@ -15043,7 +15043,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H506" t="n">
         <v>19000</v>
@@ -15217,7 +15217,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H512" t="n">
         <v>9500</v>
@@ -15449,7 +15449,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520812988281</v>
+        <v>2.38520789146423</v>
       </c>
       <c r="H520" t="n">
         <v>28500</v>
@@ -15652,7 +15652,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H530" t="n">
         <v>38000</v>
@@ -15797,7 +15797,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H532" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H533" t="n">
         <v>10000</v>
@@ -15855,7 +15855,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.29093098640442</v>
+        <v>2.290931224823</v>
       </c>
       <c r="H534" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207589149475</v>
+        <v>2.27207565307617</v>
       </c>
       <c r="H535" t="n">
         <v>23500</v>
@@ -15942,7 +15942,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H537" t="n">
         <v>39500</v>
@@ -16029,7 +16029,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H540" t="n">
         <v>27500</v>
@@ -16087,7 +16087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H542" t="n">
         <v>49000</v>
@@ -16145,7 +16145,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H544" t="n">
         <v>21500</v>
@@ -16203,7 +16203,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H546" t="n">
         <v>5500</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H547" t="n">
         <v>11500</v>
@@ -16261,7 +16261,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H548" t="n">
         <v>12000</v>
@@ -16319,7 +16319,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H550" t="n">
         <v>8000</v>
@@ -16406,7 +16406,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H553" t="n">
         <v>22500</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H559" t="n">
         <v>23500</v>
@@ -16667,7 +16667,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H562" t="n">
         <v>131000</v>
@@ -16696,7 +16696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H563" t="n">
         <v>9000</v>
@@ -16812,7 +16812,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H567" t="n">
         <v>101500</v>
@@ -16841,7 +16841,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264786720276</v>
+        <v>2.26264810562134</v>
       </c>
       <c r="H568" t="n">
         <v>69000</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H570" t="n">
         <v>27000</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H573" t="n">
         <v>18000</v>
@@ -17044,7 +17044,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H575" t="n">
         <v>27500</v>
@@ -17073,7 +17073,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H576" t="n">
         <v>19500</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H577" t="n">
         <v>31000</v>
@@ -17160,7 +17160,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H579" t="n">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066005706787</v>
+        <v>2.13066029548645</v>
       </c>
       <c r="H582" t="n">
         <v>21500</v>
@@ -17305,7 +17305,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H584" t="n">
         <v>3500</v>
@@ -17334,7 +17334,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H585" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H593" t="n">
         <v>18500</v>
@@ -17653,7 +17653,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H596" t="n">
         <v>20000</v>
@@ -17682,7 +17682,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H597" t="n">
         <v>13000</v>
@@ -17711,7 +17711,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H598" t="n">
         <v>45000</v>
@@ -17885,7 +17885,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038924694061</v>
+        <v>1.97038900852203</v>
       </c>
       <c r="H604" t="n">
         <v>50500</v>
@@ -18059,7 +18059,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082611560822</v>
+        <v>1.88082599639893</v>
       </c>
       <c r="H610" t="n">
         <v>29000</v>
@@ -80038,6 +80038,35 @@
         <v>6697</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>103148</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478422164917</v>
+        <v>2.38478398323059</v>
       </c>
       <c r="H2" t="n">
         <v>35500</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -514,7 +514,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652428627014</v>
+        <v>2.29652404785156</v>
       </c>
       <c r="H5" t="n">
         <v>20500</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595820426941</v>
+        <v>2.37595772743225</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -717,7 +717,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123684883118</v>
+        <v>2.32123708724976</v>
       </c>
       <c r="H12" t="n">
         <v>24500</v>
@@ -862,7 +862,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003791809082</v>
+        <v>2.24003767967224</v>
       </c>
       <c r="H17" t="n">
         <v>35500</v>
@@ -949,7 +949,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236045837402</v>
+        <v>2.13236021995544</v>
       </c>
       <c r="H20" t="n">
         <v>35000</v>
@@ -1007,7 +1007,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120310783386</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1065,7 +1065,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412570953369</v>
+        <v>2.13412594795227</v>
       </c>
       <c r="H24" t="n">
         <v>17000</v>
@@ -1123,7 +1123,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1152,7 +1152,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.9858490228653</v>
+        <v>1.98584914207458</v>
       </c>
       <c r="H27" t="n">
         <v>30500</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347563266754</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1210,7 +1210,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230200767517</v>
+        <v>1.92230188846588</v>
       </c>
       <c r="H29" t="n">
         <v>53000</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990355014801</v>
+        <v>1.7599036693573</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637316703796</v>
+        <v>1.75637328624725</v>
       </c>
       <c r="H32" t="n">
         <v>31000</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991210460663</v>
+        <v>1.78991198539734</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1384,7 +1384,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H35" t="n">
         <v>74000</v>
@@ -1442,7 +1442,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120310783386</v>
+        <v>2.20120334625244</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1500,7 +1500,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H39" t="n">
         <v>23000</v>
@@ -1529,7 +1529,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351804733276</v>
+        <v>2.06351780891418</v>
       </c>
       <c r="H41" t="n">
         <v>9500</v>
@@ -1674,7 +1674,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G45" t="n">
-        <v>2.16413426399231</v>
+        <v>2.16413402557373</v>
       </c>
       <c r="H45" t="n">
         <v>32500</v>
@@ -1732,7 +1732,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.10058689117432</v>
+        <v>2.1005871295929</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1761,7 +1761,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647391319275</v>
+        <v>2.11647367477417</v>
       </c>
       <c r="H48" t="n">
         <v>45500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177798271179</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824724197388</v>
+        <v>2.14824748039246</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.1270649433136</v>
+        <v>2.12706518173218</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648222923279</v>
+        <v>2.14648199081421</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300233840942</v>
+        <v>2.32300209999084</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709036827087</v>
+        <v>2.21709012985229</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297691345215</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481748580933</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2573,7 +2573,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G76" t="n">
-        <v>2.52953052520752</v>
+        <v>2.52953028678894</v>
       </c>
       <c r="H76" t="n">
         <v>98500</v>
@@ -2602,7 +2602,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.59484267234802</v>
+        <v>2.5948429107666</v>
       </c>
       <c r="H77" t="n">
         <v>59000</v>
@@ -2718,7 +2718,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723245620728</v>
+        <v>2.72723269462585</v>
       </c>
       <c r="H81" t="n">
         <v>19500</v>
@@ -2747,7 +2747,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192862510681</v>
+        <v>2.69192886352539</v>
       </c>
       <c r="H82" t="n">
         <v>91000</v>
@@ -2776,7 +2776,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.70958042144775</v>
+        <v>2.70958065986633</v>
       </c>
       <c r="H83" t="n">
         <v>24000</v>
@@ -3095,7 +3095,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3327,7 +3327,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G102" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H106" t="n">
         <v>14000</v>
@@ -3472,7 +3472,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3530,7 +3530,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G109" t="n">
-        <v>2.47104287147522</v>
+        <v>2.47104263305664</v>
       </c>
       <c r="H109" t="n">
         <v>3500</v>
@@ -3588,7 +3588,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48762702941895</v>
+        <v>2.48762726783752</v>
       </c>
       <c r="H111" t="n">
         <v>3000</v>
@@ -3617,7 +3617,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>2.48762702941895</v>
+        <v>2.48762726783752</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H116" t="n">
         <v>27000</v>
@@ -3791,7 +3791,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H118" t="n">
         <v>21500</v>
@@ -3907,7 +3907,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H123" t="n">
         <v>1500</v>
@@ -3965,7 +3965,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H124" t="n">
         <v>13500</v>
@@ -3994,7 +3994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H125" t="n">
         <v>44000</v>
@@ -4023,7 +4023,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H126" t="n">
         <v>38000</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4139,7 +4139,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H130" t="n">
         <v>22500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544834136963</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H142" t="n">
         <v>5000</v>
@@ -4632,7 +4632,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G147" t="n">
-        <v>2.31994247436523</v>
+        <v>2.31994271278381</v>
       </c>
       <c r="H147" t="n">
         <v>10500</v>
@@ -4748,7 +4748,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G151" t="n">
-        <v>2.53553700447083</v>
+        <v>2.5355372428894</v>
       </c>
       <c r="H151" t="n">
         <v>23000</v>
@@ -4835,7 +4835,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H154" t="n">
         <v>2500</v>
@@ -4864,7 +4864,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="n">
         <v>4500</v>
@@ -4922,7 +4922,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G157" t="n">
-        <v>2.31625723838806</v>
+        <v>2.31625699996948</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -5009,7 +5009,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102100372314</v>
+        <v>2.40102076530457</v>
       </c>
       <c r="H160" t="n">
         <v>3000</v>
@@ -5096,7 +5096,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G163" t="n">
-        <v>2.31994247436523</v>
+        <v>2.31994271278381</v>
       </c>
       <c r="H163" t="n">
         <v>9000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5299,7 +5299,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>2.29783034324646</v>
+        <v>2.29783010482788</v>
       </c>
       <c r="H170" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807786941528</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H172" t="n">
         <v>21000</v>
@@ -5386,7 +5386,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807786941528</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H173" t="n">
         <v>11000</v>
@@ -5415,7 +5415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807786941528</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5473,7 +5473,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097679138184</v>
+        <v>2.26097655296326</v>
       </c>
       <c r="H178" t="n">
         <v>73000</v>
@@ -5589,7 +5589,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807786941528</v>
+        <v>2.24807810783386</v>
       </c>
       <c r="H180" t="n">
         <v>43000</v>
@@ -5676,7 +5676,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H184" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H185" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517942428589</v>
+        <v>2.23517918586731</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5937,7 +5937,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H192" t="n">
         <v>11500</v>
@@ -5966,7 +5966,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G193" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H193" t="n">
         <v>35500</v>
@@ -5995,7 +5995,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H194" t="n">
         <v>7500</v>
@@ -6053,7 +6053,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H196" t="n">
         <v>17000</v>
@@ -6111,7 +6111,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H198" t="n">
         <v>20000</v>
@@ -6372,7 +6372,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731318473816</v>
+        <v>2.32731342315674</v>
       </c>
       <c r="H207" t="n">
         <v>14000</v>
@@ -6488,7 +6488,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H211" t="n">
         <v>47500</v>
@@ -6517,7 +6517,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H212" t="n">
         <v>12500</v>
@@ -6546,7 +6546,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H213" t="n">
         <v>8000</v>
@@ -6691,7 +6691,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6836,7 +6836,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H223" t="n">
         <v>500</v>
@@ -6865,7 +6865,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H224" t="n">
         <v>2500</v>
@@ -6981,7 +6981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785268783569</v>
+        <v>2.36785244941711</v>
       </c>
       <c r="H228" t="n">
         <v>4500</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7126,7 +7126,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547092437744</v>
       </c>
       <c r="H233" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.2296507358551</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915592193604</v>
+        <v>2.32915616035461</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7387,7 +7387,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32178521156311</v>
+        <v>2.32178544998169</v>
       </c>
       <c r="H242" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G243" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7445,7 +7445,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G244" t="n">
-        <v>2.30704379081726</v>
+        <v>2.30704355239868</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7822,7 +7822,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H257" t="n">
         <v>21000</v>
@@ -7851,7 +7851,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G258" t="n">
-        <v>2.56501984596252</v>
+        <v>2.5650200843811</v>
       </c>
       <c r="H258" t="n">
         <v>35000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8025,7 +8025,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477279663086</v>
+        <v>2.61477255821228</v>
       </c>
       <c r="H264" t="n">
         <v>20000</v>
@@ -8402,7 +8402,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H277" t="n">
         <v>13000</v>
@@ -8460,7 +8460,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5465931892395</v>
+        <v>2.54659295082092</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8518,7 +8518,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G281" t="n">
-        <v>2.65899682044983</v>
+        <v>2.65899705886841</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8605,7 +8605,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>2.5668625831604</v>
+        <v>2.56686282157898</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8721,7 +8721,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G288" t="n">
-        <v>2.55764937400818</v>
+        <v>2.5576491355896</v>
       </c>
       <c r="H288" t="n">
         <v>3500</v>
@@ -8895,7 +8895,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061437606812</v>
+        <v>2.78061413764954</v>
       </c>
       <c r="H294" t="n">
         <v>29000</v>
@@ -8924,7 +8924,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349119186401</v>
+        <v>2.72349095344543</v>
       </c>
       <c r="H295" t="n">
         <v>13500</v>
@@ -8982,7 +8982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>2.69032287597656</v>
+        <v>2.69032263755798</v>
       </c>
       <c r="H297" t="n">
         <v>33000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G298" t="n">
-        <v>2.71059226989746</v>
+        <v>2.71059203147888</v>
       </c>
       <c r="H298" t="n">
         <v>6000</v>
@@ -9185,7 +9185,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G304" t="n">
-        <v>2.89117550849915</v>
+        <v>2.89117574691772</v>
       </c>
       <c r="H304" t="n">
         <v>56500</v>
@@ -9446,7 +9446,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G313" t="n">
-        <v>2.88749027252197</v>
+        <v>2.88749003410339</v>
       </c>
       <c r="H313" t="n">
         <v>30500</v>
@@ -9533,7 +9533,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G316" t="n">
-        <v>2.88749027252197</v>
+        <v>2.88749003410339</v>
       </c>
       <c r="H316" t="n">
         <v>34500</v>
@@ -9591,7 +9591,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.9151303768158</v>
+        <v>2.91513061523438</v>
       </c>
       <c r="H318" t="n">
         <v>29000</v>
@@ -9620,7 +9620,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515248298645</v>
+        <v>2.98515272140503</v>
       </c>
       <c r="H319" t="n">
         <v>51500</v>
@@ -9678,7 +9678,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097219467163</v>
+        <v>3.08097243309021</v>
       </c>
       <c r="H321" t="n">
         <v>110500</v>
@@ -9765,7 +9765,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2689266204834</v>
+        <v>3.26892638206482</v>
       </c>
       <c r="H324" t="n">
         <v>81500</v>
@@ -9852,7 +9852,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G327" t="n">
-        <v>3.15652251243591</v>
+        <v>3.15652275085449</v>
       </c>
       <c r="H327" t="n">
         <v>64500</v>
@@ -9910,7 +9910,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993811607361</v>
+        <v>3.13993835449219</v>
       </c>
       <c r="H329" t="n">
         <v>22000</v>
@@ -9939,7 +9939,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937722206116</v>
+        <v>3.02937698364258</v>
       </c>
       <c r="H330" t="n">
         <v>27500</v>
@@ -10200,7 +10200,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15836501121521</v>
+        <v>3.15836524963379</v>
       </c>
       <c r="H339" t="n">
         <v>19000</v>
@@ -10258,7 +10258,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470164299011</v>
+        <v>3.22470188140869</v>
       </c>
       <c r="H341" t="n">
         <v>21500</v>
@@ -10287,7 +10287,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G342" t="n">
-        <v>3.22654461860657</v>
+        <v>3.22654485702515</v>
       </c>
       <c r="H342" t="n">
         <v>10500</v>
@@ -10577,7 +10577,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03674793243408</v>
+        <v>3.0367476940155</v>
       </c>
       <c r="H352" t="n">
         <v>22000</v>
@@ -10606,7 +10606,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G353" t="n">
-        <v>2.98330974578857</v>
+        <v>2.98330998420715</v>
       </c>
       <c r="H353" t="n">
         <v>23000</v>
@@ -10693,7 +10693,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.2676408290863</v>
+        <v>3.26764059066772</v>
       </c>
       <c r="H356" t="n">
         <v>94000</v>
@@ -10838,7 +10838,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215264320374</v>
+        <v>3.29215288162231</v>
       </c>
       <c r="H361" t="n">
         <v>33000</v>
@@ -10867,7 +10867,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279147148132</v>
+        <v>3.18279123306274</v>
       </c>
       <c r="H362" t="n">
         <v>64000</v>
@@ -10954,7 +10954,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713475227356</v>
+        <v>3.17713451385498</v>
       </c>
       <c r="H365" t="n">
         <v>20500</v>
@@ -10983,7 +10983,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491179466248</v>
+        <v>3.11491203308105</v>
       </c>
       <c r="H366" t="n">
         <v>14500</v>
@@ -11302,7 +11302,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H377" t="n">
         <v>25500</v>
@@ -11447,7 +11447,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H382" t="n">
         <v>10500</v>
@@ -11563,7 +11563,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.9225869178772</v>
+        <v>2.92258667945862</v>
       </c>
       <c r="H386" t="n">
         <v>6000</v>
@@ -11592,7 +11592,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H389" t="n">
         <v>16000</v>
@@ -11708,7 +11708,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669528961182</v>
+        <v>2.98669505119324</v>
       </c>
       <c r="H391" t="n">
         <v>16000</v>
@@ -11824,7 +11824,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864707946777</v>
+        <v>2.88864684104919</v>
       </c>
       <c r="H395" t="n">
         <v>6500</v>
@@ -11853,7 +11853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H396" t="n">
         <v>6500</v>
@@ -11911,7 +11911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H399" t="n">
         <v>5000</v>
@@ -11969,7 +11969,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332790374756</v>
+        <v>2.94332766532898</v>
       </c>
       <c r="H400" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H406" t="n">
         <v>18000</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.8283097743988</v>
+        <v>2.82831001281738</v>
       </c>
       <c r="H409" t="n">
         <v>8500</v>
@@ -12346,7 +12346,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682827949524</v>
+        <v>2.78682804107666</v>
       </c>
       <c r="H413" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002665519714</v>
+        <v>2.80002689361572</v>
       </c>
       <c r="H414" t="n">
         <v>7000</v>
@@ -12462,7 +12462,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H417" t="n">
         <v>5500</v>
@@ -12694,7 +12694,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517753601074</v>
+        <v>2.71517777442932</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12752,7 +12752,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046611785889</v>
+        <v>2.99046635627747</v>
       </c>
       <c r="H427" t="n">
         <v>411000</v>
@@ -12839,7 +12839,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H430" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H434" t="n">
         <v>36000</v>
@@ -12984,7 +12984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H435" t="n">
         <v>18000</v>
@@ -13013,7 +13013,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H436" t="n">
         <v>2500</v>
@@ -13100,7 +13100,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H439" t="n">
         <v>82500</v>
@@ -13245,7 +13245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228563308716</v>
+        <v>3.09228539466858</v>
       </c>
       <c r="H444" t="n">
         <v>47000</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.0790867805481</v>
+        <v>3.07908654212952</v>
       </c>
       <c r="H446" t="n">
         <v>25500</v>
@@ -13390,7 +13390,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928566932678</v>
+        <v>2.77928590774536</v>
       </c>
       <c r="H449" t="n">
         <v>531500</v>
@@ -13506,7 +13506,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.45497298240662</v>
+        <v>2.4549732208252</v>
       </c>
       <c r="H453" t="n">
         <v>144500</v>
@@ -13535,7 +13535,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H454" t="n">
         <v>47000</v>
@@ -13593,7 +13593,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H456" t="n">
         <v>146500</v>
@@ -13680,7 +13680,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187652587891</v>
+        <v>2.57187628746033</v>
       </c>
       <c r="H459" t="n">
         <v>26500</v>
@@ -13738,7 +13738,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238236427307</v>
+        <v>2.66238212585449</v>
       </c>
       <c r="H461" t="n">
         <v>152500</v>
@@ -13767,7 +13767,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H462" t="n">
         <v>60000</v>
@@ -13825,7 +13825,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032793998718</v>
+        <v>2.63032817840576</v>
       </c>
       <c r="H464" t="n">
         <v>17500</v>
@@ -14173,7 +14173,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.5021116733551</v>
+        <v>2.50211143493652</v>
       </c>
       <c r="H476" t="n">
         <v>49500</v>
@@ -14202,7 +14202,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891282081604</v>
+        <v>2.48891258239746</v>
       </c>
       <c r="H477" t="n">
         <v>26500</v>
@@ -14231,7 +14231,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137068748474</v>
+        <v>2.48137044906616</v>
       </c>
       <c r="H478" t="n">
         <v>74500</v>
@@ -14289,7 +14289,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H480" t="n">
         <v>32000</v>
@@ -14492,7 +14492,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217804908752</v>
+        <v>2.40217781066895</v>
       </c>
       <c r="H487" t="n">
         <v>20000</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.52473783493042</v>
+        <v>2.524738073349</v>
       </c>
       <c r="H494" t="n">
         <v>26000</v>
@@ -14724,7 +14724,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399684906006</v>
+        <v>2.50399708747864</v>
       </c>
       <c r="H495" t="n">
         <v>14500</v>
@@ -14811,7 +14811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834036827087</v>
+        <v>2.49834060668945</v>
       </c>
       <c r="H498" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005701065063</v>
+        <v>2.47005724906921</v>
       </c>
       <c r="H499" t="n">
         <v>36500</v>
@@ -14898,7 +14898,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H501" t="n">
         <v>14500</v>
@@ -15043,7 +15043,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H506" t="n">
         <v>19000</v>
@@ -15217,7 +15217,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H512" t="n">
         <v>9500</v>
@@ -15449,7 +15449,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520789146423</v>
+        <v>2.38520812988281</v>
       </c>
       <c r="H520" t="n">
         <v>28500</v>
@@ -15652,7 +15652,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H530" t="n">
         <v>38000</v>
@@ -15797,7 +15797,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H532" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H533" t="n">
         <v>10000</v>
@@ -15855,7 +15855,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.290931224823</v>
+        <v>2.29093098640442</v>
       </c>
       <c r="H534" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207565307617</v>
+        <v>2.27207589149475</v>
       </c>
       <c r="H535" t="n">
         <v>23500</v>
@@ -15942,7 +15942,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H537" t="n">
         <v>39500</v>
@@ -16029,7 +16029,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H540" t="n">
         <v>27500</v>
@@ -16087,7 +16087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H542" t="n">
         <v>49000</v>
@@ -16145,7 +16145,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H544" t="n">
         <v>21500</v>
@@ -16203,7 +16203,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H546" t="n">
         <v>5500</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H547" t="n">
         <v>11500</v>
@@ -16261,7 +16261,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H548" t="n">
         <v>12000</v>
@@ -16319,7 +16319,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H550" t="n">
         <v>8000</v>
@@ -16406,7 +16406,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H553" t="n">
         <v>22500</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H559" t="n">
         <v>23500</v>
@@ -16667,7 +16667,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H562" t="n">
         <v>131000</v>
@@ -16696,7 +16696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H563" t="n">
         <v>9000</v>
@@ -16812,7 +16812,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H567" t="n">
         <v>101500</v>
@@ -16841,7 +16841,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264810562134</v>
+        <v>2.26264786720276</v>
       </c>
       <c r="H568" t="n">
         <v>69000</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H570" t="n">
         <v>27000</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H573" t="n">
         <v>18000</v>
@@ -17044,7 +17044,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H575" t="n">
         <v>27500</v>
@@ -17073,7 +17073,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H576" t="n">
         <v>19500</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H577" t="n">
         <v>31000</v>
@@ -17160,7 +17160,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H579" t="n">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066029548645</v>
+        <v>2.13066005706787</v>
       </c>
       <c r="H582" t="n">
         <v>21500</v>
@@ -17305,7 +17305,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H584" t="n">
         <v>3500</v>
@@ -17334,7 +17334,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H585" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H593" t="n">
         <v>18500</v>
@@ -17653,7 +17653,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H596" t="n">
         <v>20000</v>
@@ -17682,7 +17682,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H597" t="n">
         <v>13000</v>
@@ -17711,7 +17711,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H598" t="n">
         <v>45000</v>
@@ -17885,7 +17885,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038900852203</v>
+        <v>1.97038924694061</v>
       </c>
       <c r="H604" t="n">
         <v>50500</v>
@@ -18059,7 +18059,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082599639893</v>
+        <v>1.88082611560822</v>
       </c>
       <c r="H610" t="n">
         <v>29000</v>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478398323059</v>
+        <v>2.38478422164917</v>
       </c>
       <c r="H2" t="n">
         <v>35500</v>
@@ -456,7 +456,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125348091125</v>
+        <v>2.38125371932983</v>
       </c>
       <c r="H3" t="n">
         <v>52000</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182787895203</v>
+        <v>2.33182811737061</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -543,7 +543,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419295310974</v>
+        <v>2.37419271469116</v>
       </c>
       <c r="H6" t="n">
         <v>20000</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771490097046</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -717,7 +717,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G12" t="n">
-        <v>2.32123708724976</v>
+        <v>2.32123684883118</v>
       </c>
       <c r="H12" t="n">
         <v>24500</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181100845337</v>
+        <v>2.27181124687195</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24003767967224</v>
+        <v>2.24003791809082</v>
       </c>
       <c r="H17" t="n">
         <v>35500</v>
@@ -891,7 +891,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28063726425171</v>
+        <v>2.28063750267029</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884682655334</v>
+        <v>2.18884706497192</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1782557964325</v>
+        <v>2.17825555801392</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1065,7 +1065,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412594795227</v>
+        <v>2.13412570953369</v>
       </c>
       <c r="H24" t="n">
         <v>17000</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347587108612</v>
+        <v>1.91347575187683</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7599036693573</v>
+        <v>1.75990343093872</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637328624725</v>
+        <v>1.75637316703796</v>
       </c>
       <c r="H32" t="n">
         <v>31000</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991198539734</v>
+        <v>1.78991210460663</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1355,7 +1355,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H34" t="n">
         <v>70500</v>
@@ -1587,7 +1587,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H42" t="n">
         <v>6500</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1732,7 +1732,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.1005871295929</v>
+        <v>2.10058689117432</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410883903503</v>
+        <v>2.07410907745361</v>
       </c>
       <c r="H50" t="n">
         <v>11500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177774429321</v>
+        <v>2.15177750587463</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -1935,7 +1935,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.12000417709351</v>
+        <v>2.12000393867493</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001273155212</v>
+        <v>2.15001249313354</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824748039246</v>
+        <v>2.14824724197388</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706518173218</v>
+        <v>2.12706542015076</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648199081421</v>
+        <v>2.14648222923279</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296004295349</v>
+        <v>2.17296028137207</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300186157227</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481748580933</v>
+        <v>2.50481772422791</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2602,7 +2602,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.5948429107666</v>
+        <v>2.59484267234802</v>
       </c>
       <c r="H77" t="n">
         <v>59000</v>
@@ -2631,7 +2631,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.61249470710754</v>
+        <v>2.61249446868896</v>
       </c>
       <c r="H78" t="n">
         <v>55000</v>
@@ -2747,7 +2747,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G82" t="n">
-        <v>2.69192886352539</v>
+        <v>2.69192862510681</v>
       </c>
       <c r="H82" t="n">
         <v>91000</v>
@@ -2863,7 +2863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H86" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H88" t="n">
         <v>42500</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H99" t="n">
         <v>2500</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3327,7 +3327,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H102" t="n">
         <v>5000</v>
@@ -3356,7 +3356,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G103" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789666175842</v>
+        <v>2.50789642333984</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G109" t="n">
-        <v>2.47104263305664</v>
+        <v>2.47104287147522</v>
       </c>
       <c r="H109" t="n">
         <v>3500</v>
@@ -3559,7 +3559,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841382026672</v>
+        <v>2.47841358184814</v>
       </c>
       <c r="H110" t="n">
         <v>3000</v>
@@ -3878,7 +3878,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G121" t="n">
-        <v>2.34205508232117</v>
+        <v>2.34205484390259</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544857978821</v>
+        <v>2.25544881820679</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252779006958</v>
+        <v>2.17252802848816</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4748,7 +4748,7 @@
         <v>2.75200009346008</v>
       </c>
       <c r="G151" t="n">
-        <v>2.5355372428894</v>
+        <v>2.53553700447083</v>
       </c>
       <c r="H151" t="n">
         <v>23000</v>
@@ -4777,7 +4777,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H152" t="n">
         <v>13000</v>
@@ -4864,7 +4864,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.43418908119202</v>
+        <v>2.4341893196106</v>
       </c>
       <c r="H155" t="n">
         <v>4500</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -4922,7 +4922,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G157" t="n">
-        <v>2.31625699996948</v>
+        <v>2.31625723838806</v>
       </c>
       <c r="H157" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>2.31441473960876</v>
+        <v>2.31441450119019</v>
       </c>
       <c r="H164" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888628959656</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5299,7 +5299,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G170" t="n">
-        <v>2.29783010482788</v>
+        <v>2.29783034324646</v>
       </c>
       <c r="H170" t="n">
         <v>1500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6169,7 +6169,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37706589698792</v>
+        <v>2.37706565856934</v>
       </c>
       <c r="H200" t="n">
         <v>6500</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6778,7 +6778,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338066101074</v>
+        <v>2.37338042259216</v>
       </c>
       <c r="H221" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888628959656</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7126,7 +7126,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547092437744</v>
+        <v>2.32547068595886</v>
       </c>
       <c r="H233" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.2296507358551</v>
+        <v>2.22965097427368</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7764,7 +7764,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>2.37706589698792</v>
+        <v>2.37706565856934</v>
       </c>
       <c r="H255" t="n">
         <v>19500</v>
@@ -7880,7 +7880,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G259" t="n">
-        <v>2.56317734718323</v>
+        <v>2.56317710876465</v>
       </c>
       <c r="H259" t="n">
         <v>20000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054829597473</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8431,7 +8431,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.56133460998535</v>
+        <v>2.56133437156677</v>
       </c>
       <c r="H278" t="n">
         <v>6500</v>
@@ -8518,7 +8518,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G281" t="n">
-        <v>2.65899705886841</v>
+        <v>2.65899682044983</v>
       </c>
       <c r="H281" t="n">
         <v>10000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>2.67189574241638</v>
+        <v>2.67189598083496</v>
       </c>
       <c r="H289" t="n">
         <v>59000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G304" t="n">
-        <v>2.89117574691772</v>
+        <v>2.89117550849915</v>
       </c>
       <c r="H304" t="n">
         <v>56500</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616445541382</v>
+        <v>2.85616421699524</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9301,7 +9301,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G308" t="n">
-        <v>2.81746816635132</v>
+        <v>2.8174684047699</v>
       </c>
       <c r="H308" t="n">
         <v>9000</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G313" t="n">
-        <v>2.88749003410339</v>
+        <v>2.88749027252197</v>
       </c>
       <c r="H313" t="n">
         <v>30500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9533,7 +9533,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G316" t="n">
-        <v>2.88749003410339</v>
+        <v>2.88749027252197</v>
       </c>
       <c r="H316" t="n">
         <v>34500</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.27076888084412</v>
+        <v>3.2707691192627</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9852,7 +9852,7 @@
         <v>3.42600011825562</v>
       </c>
       <c r="G327" t="n">
-        <v>3.15652275085449</v>
+        <v>3.15652251243591</v>
       </c>
       <c r="H327" t="n">
         <v>64500</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10200,7 +10200,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G339" t="n">
-        <v>3.15836524963379</v>
+        <v>3.15836501121521</v>
       </c>
       <c r="H339" t="n">
         <v>19000</v>
@@ -10287,7 +10287,7 @@
         <v>3.50200009346008</v>
       </c>
       <c r="G342" t="n">
-        <v>3.22654485702515</v>
+        <v>3.22654461860657</v>
       </c>
       <c r="H342" t="n">
         <v>10500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10461,7 +10461,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099430084229</v>
+        <v>3.15099453926086</v>
       </c>
       <c r="H348" t="n">
         <v>9500</v>
@@ -10490,7 +10490,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441014289856</v>
+        <v>3.13441038131714</v>
       </c>
       <c r="H349" t="n">
         <v>16000</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045527458191</v>
+        <v>3.11045503616333</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10635,7 +10635,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>3.04043316841125</v>
+        <v>3.04043292999268</v>
       </c>
       <c r="H354" t="n">
         <v>15000</v>
@@ -80067,6 +80067,64 @@
         <v>103148</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.326999992132187</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>3615</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125371932983</v>
+        <v>2.38125348091125</v>
       </c>
       <c r="H3" t="n">
         <v>52000</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -543,7 +543,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419271469116</v>
+        <v>2.37419295310974</v>
       </c>
       <c r="H6" t="n">
         <v>20000</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595772743225</v>
+        <v>2.37595796585083</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -804,7 +804,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062894821167</v>
+        <v>2.25062870979309</v>
       </c>
       <c r="H15" t="n">
         <v>27500</v>
@@ -891,7 +891,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G18" t="n">
-        <v>2.28063750267029</v>
+        <v>2.28063726425171</v>
       </c>
       <c r="H18" t="n">
         <v>10000</v>
@@ -949,7 +949,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236021995544</v>
+        <v>2.13236045837402</v>
       </c>
       <c r="H20" t="n">
         <v>35000</v>
@@ -1152,7 +1152,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584914207458</v>
+        <v>1.98584926128387</v>
       </c>
       <c r="H27" t="n">
         <v>30500</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347575187683</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1471,7 +1471,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.15354299545288</v>
+        <v>2.1535427570343</v>
       </c>
       <c r="H38" t="n">
         <v>21000</v>
@@ -1558,7 +1558,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351804733276</v>
       </c>
       <c r="H41" t="n">
         <v>9500</v>
@@ -1732,7 +1732,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.10058689117432</v>
+        <v>2.1005871295929</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177750587463</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.07587432861328</v>
+        <v>2.0758740901947</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -1935,7 +1935,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.12000393867493</v>
+        <v>2.12000417709351</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824724197388</v>
+        <v>2.14824748039246</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706542015076</v>
+        <v>2.12706518173218</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530800819397</v>
+        <v>2.15530824661255</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648222923279</v>
+        <v>2.14648175239563</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="n">
         <v>12000</v>
@@ -2196,7 +2196,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H63" t="n">
         <v>46500</v>
@@ -2225,7 +2225,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>2.36360192298889</v>
+        <v>2.36360168457031</v>
       </c>
       <c r="H64" t="n">
         <v>20500</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534174919128</v>
+        <v>2.27534151077271</v>
       </c>
       <c r="H69" t="n">
         <v>6500</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481748580933</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2544,7 +2544,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542562484741</v>
+        <v>2.57542538642883</v>
       </c>
       <c r="H75" t="n">
         <v>29500</v>
@@ -2631,7 +2631,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G78" t="n">
-        <v>2.61249446868896</v>
+        <v>2.61249470710754</v>
       </c>
       <c r="H78" t="n">
         <v>55000</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2776,7 +2776,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.70958065986633</v>
+        <v>2.70958042144775</v>
       </c>
       <c r="H83" t="n">
         <v>24000</v>
@@ -2805,7 +2805,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G84" t="n">
-        <v>2.67604207992554</v>
+        <v>2.67604184150696</v>
       </c>
       <c r="H84" t="n">
         <v>32500</v>
@@ -2863,7 +2863,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G86" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H86" t="n">
         <v>20000</v>
@@ -2921,7 +2921,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G88" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H88" t="n">
         <v>42500</v>
@@ -2950,7 +2950,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -3066,7 +3066,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="n">
         <v>5500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3240,7 +3240,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G99" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H99" t="n">
         <v>2500</v>
@@ -3414,7 +3414,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="n">
         <v>15500</v>
@@ -3559,7 +3559,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841358184814</v>
+        <v>2.47841382026672</v>
       </c>
       <c r="H110" t="n">
         <v>3000</v>
@@ -3588,7 +3588,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H111" t="n">
         <v>3000</v>
@@ -3617,7 +3617,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G112" t="n">
-        <v>2.48762726783752</v>
+        <v>2.48762702941895</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -3878,7 +3878,7 @@
         <v>2.54200005531311</v>
       </c>
       <c r="G121" t="n">
-        <v>2.34205484390259</v>
+        <v>2.34205508232117</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4255,7 +4255,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544881820679</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G147" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H147" t="n">
         <v>10500</v>
@@ -4690,7 +4690,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="n">
         <v>16000</v>
@@ -4719,7 +4719,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="n">
         <v>1000</v>
@@ -4777,7 +4777,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G152" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H152" t="n">
         <v>13000</v>
@@ -4835,7 +4835,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H154" t="n">
         <v>2500</v>
@@ -5096,7 +5096,7 @@
         <v>2.51799988746643</v>
       </c>
       <c r="G163" t="n">
-        <v>2.31994271278381</v>
+        <v>2.31994247436523</v>
       </c>
       <c r="H163" t="n">
         <v>9000</v>
@@ -5125,7 +5125,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G164" t="n">
-        <v>2.31441450119019</v>
+        <v>2.31441473960876</v>
       </c>
       <c r="H164" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5357,7 +5357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H172" t="n">
         <v>21000</v>
@@ -5386,7 +5386,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H173" t="n">
         <v>11000</v>
@@ -5415,7 +5415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5589,7 +5589,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807810783386</v>
+        <v>2.24807786941528</v>
       </c>
       <c r="H180" t="n">
         <v>43000</v>
@@ -5966,7 +5966,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G193" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H193" t="n">
         <v>35500</v>
@@ -5995,7 +5995,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H194" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="n">
         <v>65000</v>
@@ -6111,7 +6111,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H198" t="n">
         <v>20000</v>
@@ -6169,7 +6169,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H200" t="n">
         <v>6500</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758305549622</v>
+        <v>2.34758281707764</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890863418579</v>
+        <v>2.37890887260437</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6546,7 +6546,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.44156002998352</v>
+        <v>2.4415602684021</v>
       </c>
       <c r="H213" t="n">
         <v>8000</v>
@@ -6691,7 +6691,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6778,7 +6778,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338042259216</v>
+        <v>2.37338066101074</v>
       </c>
       <c r="H221" t="n">
         <v>6000</v>
@@ -6952,7 +6952,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="n">
         <v>8500</v>
@@ -7039,7 +7039,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888628959656</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7387,7 +7387,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G242" t="n">
-        <v>2.32178544998169</v>
+        <v>2.32178521156311</v>
       </c>
       <c r="H242" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G243" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H243" t="n">
         <v>3500</v>
@@ -7445,7 +7445,7 @@
         <v>2.50399994850159</v>
       </c>
       <c r="G244" t="n">
-        <v>2.30704355239868</v>
+        <v>2.30704379081726</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7764,7 +7764,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G255" t="n">
-        <v>2.37706565856934</v>
+        <v>2.37706589698792</v>
       </c>
       <c r="H255" t="n">
         <v>19500</v>
@@ -7851,7 +7851,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G258" t="n">
-        <v>2.5650200843811</v>
+        <v>2.56501984596252</v>
       </c>
       <c r="H258" t="n">
         <v>35000</v>
@@ -7880,7 +7880,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G259" t="n">
-        <v>2.56317710876465</v>
+        <v>2.56317734718323</v>
       </c>
       <c r="H259" t="n">
         <v>20000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054829597473</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663716316223</v>
+        <v>2.68663692474365</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8286,7 +8286,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="n">
         <v>13000</v>
@@ -8431,7 +8431,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G278" t="n">
-        <v>2.56133437156677</v>
+        <v>2.56133460998535</v>
       </c>
       <c r="H278" t="n">
         <v>6500</v>
@@ -8460,7 +8460,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.54659295082092</v>
+        <v>2.5465931892395</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8605,7 +8605,7 @@
         <v>2.78600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>2.56686282157898</v>
+        <v>2.5668625831604</v>
       </c>
       <c r="H284" t="n">
         <v>6500</v>
@@ -8634,7 +8634,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="n">
         <v>8500</v>
@@ -8692,7 +8692,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>2.77600002288818</v>
       </c>
       <c r="G288" t="n">
-        <v>2.5576491355896</v>
+        <v>2.55764937400818</v>
       </c>
       <c r="H288" t="n">
         <v>3500</v>
@@ -8750,7 +8750,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G289" t="n">
-        <v>2.67189598083496</v>
+        <v>2.67189574241638</v>
       </c>
       <c r="H289" t="n">
         <v>59000</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8924,7 +8924,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349095344543</v>
+        <v>2.72349119186401</v>
       </c>
       <c r="H295" t="n">
         <v>13500</v>
@@ -8982,7 +8982,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G297" t="n">
-        <v>2.69032263755798</v>
+        <v>2.69032287597656</v>
       </c>
       <c r="H297" t="n">
         <v>33000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G298" t="n">
-        <v>2.71059203147888</v>
+        <v>2.71059226989746</v>
       </c>
       <c r="H298" t="n">
         <v>6000</v>
@@ -9301,7 +9301,7 @@
         <v>3.05800008773804</v>
       </c>
       <c r="G308" t="n">
-        <v>2.8174684047699</v>
+        <v>2.81746816635132</v>
       </c>
       <c r="H308" t="n">
         <v>9000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088376998901</v>
+        <v>2.80088400840759</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9649,7 +9649,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="n">
         <v>33500</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202837944031</v>
+        <v>3.09202861785889</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9968,7 +9968,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -10084,7 +10084,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="n">
         <v>9500</v>
@@ -10461,7 +10461,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099453926086</v>
+        <v>3.15099430084229</v>
       </c>
       <c r="H348" t="n">
         <v>9500</v>
@@ -10490,7 +10490,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441038131714</v>
+        <v>3.13441014289856</v>
       </c>
       <c r="H349" t="n">
         <v>16000</v>
@@ -10606,7 +10606,7 @@
         <v>3.23799991607666</v>
       </c>
       <c r="G353" t="n">
-        <v>2.98330998420715</v>
+        <v>2.98330974578857</v>
       </c>
       <c r="H353" t="n">
         <v>23000</v>
@@ -10635,7 +10635,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G354" t="n">
-        <v>3.04043292999268</v>
+        <v>3.04043316841125</v>
       </c>
       <c r="H354" t="n">
         <v>15000</v>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478422164917</v>
+        <v>2.38478398323059</v>
       </c>
       <c r="H2" t="n">
         <v>35500</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182787895203</v>
+        <v>2.33182811737061</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -543,7 +543,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419295310974</v>
+        <v>2.37419319152832</v>
       </c>
       <c r="H6" t="n">
         <v>20000</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771490097046</v>
+        <v>2.34771466255188</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -630,7 +630,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G9" t="n">
-        <v>2.34948015213013</v>
+        <v>2.34947991371155</v>
       </c>
       <c r="H9" t="n">
         <v>4500</v>
@@ -688,7 +688,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828953742981</v>
+        <v>2.29828929901123</v>
       </c>
       <c r="H11" t="n">
         <v>26500</v>
@@ -746,7 +746,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299378395081</v>
+        <v>2.29299354553223</v>
       </c>
       <c r="H13" t="n">
         <v>49000</v>
@@ -804,7 +804,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062870979309</v>
+        <v>2.25062894821167</v>
       </c>
       <c r="H15" t="n">
         <v>27500</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181124687195</v>
+        <v>2.27181100845337</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884706497192</v>
+        <v>2.18884682655334</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17825555801392</v>
+        <v>2.1782557964325</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1152,7 +1152,7 @@
         <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.98584926128387</v>
+        <v>1.9858490228653</v>
       </c>
       <c r="H27" t="n">
         <v>30500</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347587108612</v>
+        <v>1.91347575187683</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1210,7 +1210,7 @@
         <v>2.17799997329712</v>
       </c>
       <c r="G29" t="n">
-        <v>1.92230188846588</v>
+        <v>1.92230176925659</v>
       </c>
       <c r="H29" t="n">
         <v>53000</v>
@@ -1239,7 +1239,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G30" t="n">
-        <v>1.77932071685791</v>
+        <v>1.7793208360672</v>
       </c>
       <c r="H30" t="n">
         <v>130500</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990343093872</v>
+        <v>1.75990355014801</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637316703796</v>
+        <v>1.75637304782867</v>
       </c>
       <c r="H32" t="n">
         <v>31000</v>
@@ -1326,7 +1326,7 @@
         <v>2.02800011634827</v>
       </c>
       <c r="G33" t="n">
-        <v>1.78991210460663</v>
+        <v>1.78991198539734</v>
       </c>
       <c r="H33" t="n">
         <v>147000</v>
@@ -1471,7 +1471,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1535427570343</v>
+        <v>2.15354299545288</v>
       </c>
       <c r="H38" t="n">
         <v>21000</v>
@@ -1558,7 +1558,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351804733276</v>
+        <v>2.06351780891418</v>
       </c>
       <c r="H41" t="n">
         <v>9500</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1848,7 +1848,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G51" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H51" t="n">
         <v>1000</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177774429321</v>
+        <v>2.15177798271179</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1906,7 +1906,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0758740901947</v>
+        <v>2.07587432861328</v>
       </c>
       <c r="H53" t="n">
         <v>4500</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001273155212</v>
+        <v>2.15001249313354</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824748039246</v>
+        <v>2.14824724197388</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706518173218</v>
+        <v>2.1270649433136</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648175239563</v>
+        <v>2.14648222923279</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296004295349</v>
+        <v>2.17296028137207</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300186157227</v>
+        <v>2.32300209999084</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534151077271</v>
+        <v>2.27534174919128</v>
       </c>
       <c r="H69" t="n">
         <v>6500</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297667503357</v>
+        <v>2.23297715187073</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481748580933</v>
+        <v>2.50481772422791</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423453330994</v>
+        <v>2.52423477172852</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2544,7 +2544,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542538642883</v>
+        <v>2.57542562484741</v>
       </c>
       <c r="H75" t="n">
         <v>29500</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664142608643</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723269462585</v>
+        <v>2.72723245620728</v>
       </c>
       <c r="H81" t="n">
         <v>19500</v>
@@ -2776,7 +2776,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>2.70958042144775</v>
+        <v>2.70958065986633</v>
       </c>
       <c r="H83" t="n">
         <v>24000</v>
@@ -2805,7 +2805,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G84" t="n">
-        <v>2.67604184150696</v>
+        <v>2.67604207992554</v>
       </c>
       <c r="H84" t="n">
         <v>32500</v>
@@ -2950,7 +2950,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3066,7 +3066,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582874298096</v>
+        <v>2.62582850456238</v>
       </c>
       <c r="H93" t="n">
         <v>5500</v>
@@ -3095,7 +3095,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.57423329353333</v>
+        <v>2.5742335319519</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789642333984</v>
+        <v>2.50789666175842</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3414,7 +3414,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605392456055</v>
+        <v>2.50605416297913</v>
       </c>
       <c r="H105" t="n">
         <v>15500</v>
@@ -3443,7 +3443,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H106" t="n">
         <v>14000</v>
@@ -3472,7 +3472,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -3733,7 +3733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H116" t="n">
         <v>27000</v>
@@ -3791,7 +3791,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H118" t="n">
         <v>21500</v>
@@ -3907,7 +3907,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H123" t="n">
         <v>1500</v>
@@ -3965,7 +3965,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H124" t="n">
         <v>13500</v>
@@ -3994,7 +3994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H125" t="n">
         <v>44000</v>
@@ -4023,7 +4023,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H126" t="n">
         <v>38000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4139,7 +4139,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H130" t="n">
         <v>22500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4255,7 +4255,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753884315491</v>
+        <v>2.20753860473633</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544857978821</v>
+        <v>2.25544834136963</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252802848816</v>
+        <v>2.17252779006958</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4487,7 +4487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H142" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228026390076</v>
+        <v>2.22228002548218</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H149" t="n">
         <v>16000</v>
@@ -4719,7 +4719,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760492324829</v>
+        <v>2.41760516166687</v>
       </c>
       <c r="H150" t="n">
         <v>1000</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -5009,7 +5009,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102076530457</v>
+        <v>2.40102100372314</v>
       </c>
       <c r="H160" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5473,7 +5473,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097655296326</v>
+        <v>2.26097679138184</v>
       </c>
       <c r="H178" t="n">
         <v>73000</v>
@@ -5676,7 +5676,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H184" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H185" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517918586731</v>
+        <v>2.23517942428589</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19463992118835</v>
+        <v>2.19464015960693</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279718399048</v>
+        <v>2.19279742240906</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5937,7 +5937,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H192" t="n">
         <v>11500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389758110046</v>
+        <v>2.34389734268188</v>
       </c>
       <c r="H196" t="n">
         <v>17000</v>
@@ -6082,7 +6082,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H197" t="n">
         <v>65000</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758281707764</v>
+        <v>2.34758305549622</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6372,7 +6372,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731342315674</v>
+        <v>2.32731318473816</v>
       </c>
       <c r="H207" t="n">
         <v>14000</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890887260437</v>
+        <v>2.37890863418579</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6488,7 +6488,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H211" t="n">
         <v>47500</v>
@@ -6517,7 +6517,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684071540833</v>
+        <v>2.49684047698975</v>
       </c>
       <c r="H212" t="n">
         <v>12500</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996458053589</v>
+        <v>2.38996481895447</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627934455872</v>
+        <v>2.38627910614014</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6836,7 +6836,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H223" t="n">
         <v>500</v>
@@ -6865,7 +6865,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866110801697</v>
+        <v>2.42866086959839</v>
       </c>
       <c r="H224" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H227" t="n">
         <v>8500</v>
@@ -6981,7 +6981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785244941711</v>
+        <v>2.36785268783569</v>
       </c>
       <c r="H228" t="n">
         <v>4500</v>
@@ -7039,7 +7039,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180755615234</v>
+        <v>2.39180731773376</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888652801514</v>
+        <v>2.30888676643372</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965121269226</v>
+        <v>2.22965097427368</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7358,7 +7358,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915616035461</v>
+        <v>2.32915592193604</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021210670471</v>
+        <v>2.34021234512329</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7822,7 +7822,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H257" t="n">
         <v>21000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8025,7 +8025,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477255821228</v>
+        <v>2.61477279663086</v>
       </c>
       <c r="H264" t="n">
         <v>20000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715432167053</v>
+        <v>2.65715456008911</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663692474365</v>
+        <v>2.68663716316223</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8286,7 +8286,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.6442551612854</v>
+        <v>2.64425539970398</v>
       </c>
       <c r="H273" t="n">
         <v>13000</v>
@@ -8402,7 +8402,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740160942078</v>
+        <v>2.60740184783936</v>
       </c>
       <c r="H277" t="n">
         <v>13000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845803260803</v>
+        <v>2.61845779418945</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8634,7 +8634,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657108306885</v>
+        <v>2.47657084465027</v>
       </c>
       <c r="H285" t="n">
         <v>8500</v>
@@ -8692,7 +8692,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.51711010932922</v>
+        <v>2.5171103477478</v>
       </c>
       <c r="H287" t="n">
         <v>5000</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8895,7 +8895,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061413764954</v>
+        <v>2.78061437606812</v>
       </c>
       <c r="H294" t="n">
         <v>29000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169242858887</v>
+        <v>2.86169266700745</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616421699524</v>
+        <v>2.85616445541382</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088400840759</v>
+        <v>2.80088376998901</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036684989929</v>
+        <v>2.83036708831787</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9591,7 +9591,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.91513061523438</v>
+        <v>2.9151303768158</v>
       </c>
       <c r="H318" t="n">
         <v>29000</v>
@@ -9620,7 +9620,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515272140503</v>
+        <v>2.98515248298645</v>
       </c>
       <c r="H319" t="n">
         <v>51500</v>
@@ -9649,7 +9649,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780411720276</v>
+        <v>3.04780387878418</v>
       </c>
       <c r="H320" t="n">
         <v>33500</v>
@@ -9678,7 +9678,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097243309021</v>
+        <v>3.08097219467163</v>
       </c>
       <c r="H321" t="n">
         <v>110500</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202861785889</v>
+        <v>3.09202837944031</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9765,7 +9765,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.26892638206482</v>
+        <v>3.2689266204834</v>
       </c>
       <c r="H324" t="n">
         <v>81500</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.2707691192627</v>
+        <v>3.27076888084412</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9910,7 +9910,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993835449219</v>
+        <v>3.13993811607361</v>
       </c>
       <c r="H329" t="n">
         <v>22000</v>
@@ -9939,7 +9939,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937698364258</v>
+        <v>3.02937722206116</v>
       </c>
       <c r="H330" t="n">
         <v>27500</v>
@@ -9968,7 +9968,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.0072648525238</v>
+        <v>3.00726461410522</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10084,7 +10084,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964661598206</v>
+        <v>3.04964637756348</v>
       </c>
       <c r="H335" t="n">
         <v>9500</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650040626526</v>
+        <v>3.08650016784668</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10258,7 +10258,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470188140869</v>
+        <v>3.22470164299011</v>
       </c>
       <c r="H341" t="n">
         <v>21500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414074897766</v>
+        <v>3.11414051055908</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151145935059</v>
+        <v>3.12151122093201</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045503616333</v>
+        <v>3.11045527458191</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10577,7 +10577,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0367476940155</v>
+        <v>3.03674793243408</v>
       </c>
       <c r="H352" t="n">
         <v>22000</v>
@@ -10693,7 +10693,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.26764059066772</v>
+        <v>3.2676408290863</v>
       </c>
       <c r="H356" t="n">
         <v>94000</v>
@@ -10838,7 +10838,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215288162231</v>
+        <v>3.29215264320374</v>
       </c>
       <c r="H361" t="n">
         <v>33000</v>
@@ -10867,7 +10867,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279123306274</v>
+        <v>3.18279147148132</v>
       </c>
       <c r="H362" t="n">
         <v>64000</v>
@@ -10954,7 +10954,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713451385498</v>
+        <v>3.17713475227356</v>
       </c>
       <c r="H365" t="n">
         <v>20500</v>
@@ -10983,7 +10983,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491203308105</v>
+        <v>3.11491179466248</v>
       </c>
       <c r="H366" t="n">
         <v>14500</v>
@@ -11302,7 +11302,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H377" t="n">
         <v>25500</v>
@@ -11447,7 +11447,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H382" t="n">
         <v>10500</v>
@@ -11563,7 +11563,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.92258667945862</v>
+        <v>2.9225869178772</v>
       </c>
       <c r="H386" t="n">
         <v>6000</v>
@@ -11592,7 +11592,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H389" t="n">
         <v>16000</v>
@@ -11708,7 +11708,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669505119324</v>
+        <v>2.98669528961182</v>
       </c>
       <c r="H391" t="n">
         <v>16000</v>
@@ -11824,7 +11824,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864684104919</v>
+        <v>2.88864707946777</v>
       </c>
       <c r="H395" t="n">
         <v>6500</v>
@@ -11853,7 +11853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H396" t="n">
         <v>6500</v>
@@ -11911,7 +11911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H399" t="n">
         <v>5000</v>
@@ -11969,7 +11969,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332766532898</v>
+        <v>2.94332790374756</v>
       </c>
       <c r="H400" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H406" t="n">
         <v>18000</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.82831001281738</v>
+        <v>2.8283097743988</v>
       </c>
       <c r="H409" t="n">
         <v>8500</v>
@@ -12346,7 +12346,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682804107666</v>
+        <v>2.78682827949524</v>
       </c>
       <c r="H413" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002689361572</v>
+        <v>2.80002665519714</v>
       </c>
       <c r="H414" t="n">
         <v>7000</v>
@@ -12462,7 +12462,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H417" t="n">
         <v>5500</v>
@@ -12694,7 +12694,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517777442932</v>
+        <v>2.71517753601074</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12752,7 +12752,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046635627747</v>
+        <v>2.99046611785889</v>
       </c>
       <c r="H427" t="n">
         <v>411000</v>
@@ -12839,7 +12839,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H430" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H434" t="n">
         <v>36000</v>
@@ -12984,7 +12984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H435" t="n">
         <v>18000</v>
@@ -13013,7 +13013,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H436" t="n">
         <v>2500</v>
@@ -13100,7 +13100,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H439" t="n">
         <v>82500</v>
@@ -13245,7 +13245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228539466858</v>
+        <v>3.09228563308716</v>
       </c>
       <c r="H444" t="n">
         <v>47000</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.07908654212952</v>
+        <v>3.0790867805481</v>
       </c>
       <c r="H446" t="n">
         <v>25500</v>
@@ -13390,7 +13390,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928590774536</v>
+        <v>2.77928566932678</v>
       </c>
       <c r="H449" t="n">
         <v>531500</v>
@@ -13506,7 +13506,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.4549732208252</v>
+        <v>2.45497298240662</v>
       </c>
       <c r="H453" t="n">
         <v>144500</v>
@@ -13535,7 +13535,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H454" t="n">
         <v>47000</v>
@@ -13593,7 +13593,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H456" t="n">
         <v>146500</v>
@@ -13680,7 +13680,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187628746033</v>
+        <v>2.57187652587891</v>
       </c>
       <c r="H459" t="n">
         <v>26500</v>
@@ -13738,7 +13738,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238212585449</v>
+        <v>2.66238236427307</v>
       </c>
       <c r="H461" t="n">
         <v>152500</v>
@@ -13767,7 +13767,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H462" t="n">
         <v>60000</v>
@@ -13825,7 +13825,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032817840576</v>
+        <v>2.63032793998718</v>
       </c>
       <c r="H464" t="n">
         <v>17500</v>
@@ -14173,7 +14173,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.50211143493652</v>
+        <v>2.5021116733551</v>
       </c>
       <c r="H476" t="n">
         <v>49500</v>
@@ -14202,7 +14202,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891258239746</v>
+        <v>2.48891282081604</v>
       </c>
       <c r="H477" t="n">
         <v>26500</v>
@@ -14231,7 +14231,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137044906616</v>
+        <v>2.48137068748474</v>
       </c>
       <c r="H478" t="n">
         <v>74500</v>
@@ -14289,7 +14289,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H480" t="n">
         <v>32000</v>
@@ -14492,7 +14492,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217781066895</v>
+        <v>2.40217804908752</v>
       </c>
       <c r="H487" t="n">
         <v>20000</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.524738073349</v>
+        <v>2.52473783493042</v>
       </c>
       <c r="H494" t="n">
         <v>26000</v>
@@ -14724,7 +14724,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399708747864</v>
+        <v>2.50399684906006</v>
       </c>
       <c r="H495" t="n">
         <v>14500</v>
@@ -14811,7 +14811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834060668945</v>
+        <v>2.49834036827087</v>
       </c>
       <c r="H498" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005724906921</v>
+        <v>2.47005701065063</v>
       </c>
       <c r="H499" t="n">
         <v>36500</v>
@@ -14898,7 +14898,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H501" t="n">
         <v>14500</v>
@@ -15043,7 +15043,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H506" t="n">
         <v>19000</v>
@@ -15217,7 +15217,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H512" t="n">
         <v>9500</v>
@@ -15449,7 +15449,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520812988281</v>
+        <v>2.38520789146423</v>
       </c>
       <c r="H520" t="n">
         <v>28500</v>
@@ -15652,7 +15652,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H530" t="n">
         <v>38000</v>
@@ -15797,7 +15797,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H532" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H533" t="n">
         <v>10000</v>
@@ -15855,7 +15855,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.29093098640442</v>
+        <v>2.290931224823</v>
       </c>
       <c r="H534" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207589149475</v>
+        <v>2.27207565307617</v>
       </c>
       <c r="H535" t="n">
         <v>23500</v>
@@ -15942,7 +15942,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H537" t="n">
         <v>39500</v>
@@ -16029,7 +16029,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H540" t="n">
         <v>27500</v>
@@ -16087,7 +16087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H542" t="n">
         <v>49000</v>
@@ -16145,7 +16145,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H544" t="n">
         <v>21500</v>
@@ -16203,7 +16203,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H546" t="n">
         <v>5500</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H547" t="n">
         <v>11500</v>
@@ -16261,7 +16261,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H548" t="n">
         <v>12000</v>
@@ -16319,7 +16319,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H550" t="n">
         <v>8000</v>
@@ -16406,7 +16406,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H553" t="n">
         <v>22500</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H559" t="n">
         <v>23500</v>
@@ -16667,7 +16667,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H562" t="n">
         <v>131000</v>
@@ -16696,7 +16696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H563" t="n">
         <v>9000</v>
@@ -16812,7 +16812,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H567" t="n">
         <v>101500</v>
@@ -16841,7 +16841,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264786720276</v>
+        <v>2.26264810562134</v>
       </c>
       <c r="H568" t="n">
         <v>69000</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H570" t="n">
         <v>27000</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H573" t="n">
         <v>18000</v>
@@ -17044,7 +17044,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H575" t="n">
         <v>27500</v>
@@ -17073,7 +17073,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H576" t="n">
         <v>19500</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H577" t="n">
         <v>31000</v>
@@ -17160,7 +17160,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H579" t="n">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066005706787</v>
+        <v>2.13066029548645</v>
       </c>
       <c r="H582" t="n">
         <v>21500</v>
@@ -17305,7 +17305,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H584" t="n">
         <v>3500</v>
@@ -17334,7 +17334,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H585" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H593" t="n">
         <v>18500</v>
@@ -17653,7 +17653,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H596" t="n">
         <v>20000</v>
@@ -17682,7 +17682,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H597" t="n">
         <v>13000</v>
@@ -17711,7 +17711,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H598" t="n">
         <v>45000</v>
@@ -17885,7 +17885,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038924694061</v>
+        <v>1.97038900852203</v>
       </c>
       <c r="H604" t="n">
         <v>50500</v>
@@ -18059,7 +18059,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082611560822</v>
+        <v>1.88082599639893</v>
       </c>
       <c r="H610" t="n">
         <v>29000</v>
@@ -80125,6 +80125,64 @@
         <v>3615</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.333999991416931</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.333999991416931</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.333999991416931</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>600</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652404785156</v>
+        <v>2.29652380943298</v>
       </c>
       <c r="H5" t="n">
         <v>20500</v>
@@ -543,7 +543,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419319152832</v>
+        <v>2.37419295310974</v>
       </c>
       <c r="H6" t="n">
         <v>20000</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771466255188</v>
+        <v>2.34771490097046</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595796585083</v>
+        <v>2.37595772743225</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -688,7 +688,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828929901123</v>
+        <v>2.29828953742981</v>
       </c>
       <c r="H11" t="n">
         <v>26500</v>
@@ -746,7 +746,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299354553223</v>
+        <v>2.29299378395081</v>
       </c>
       <c r="H13" t="n">
         <v>49000</v>
@@ -833,7 +833,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27181100845337</v>
+        <v>2.27181124687195</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -920,7 +920,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475879669189</v>
+        <v>2.29475855827332</v>
       </c>
       <c r="H19" t="n">
         <v>1500</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884682655334</v>
+        <v>2.18884706497192</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1782557964325</v>
+        <v>2.17825555801392</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1094,7 +1094,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>2.13589096069336</v>
+        <v>2.13589119911194</v>
       </c>
       <c r="H25" t="n">
         <v>6000</v>
@@ -1123,7 +1123,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G26" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H26" t="n">
         <v>15000</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347575187683</v>
+        <v>1.91347599029541</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990355014801</v>
+        <v>1.75990343093872</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1297,7 +1297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G32" t="n">
-        <v>1.75637304782867</v>
+        <v>1.75637316703796</v>
       </c>
       <c r="H32" t="n">
         <v>31000</v>
@@ -1384,7 +1384,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G35" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H35" t="n">
         <v>74000</v>
@@ -1500,7 +1500,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G39" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H39" t="n">
         <v>23000</v>
@@ -1529,7 +1529,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G40" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.13589096069336</v>
+        <v>2.13589119911194</v>
       </c>
       <c r="H43" t="n">
         <v>16000</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1703,7 +1703,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.13589096069336</v>
+        <v>2.13589119911194</v>
       </c>
       <c r="H46" t="n">
         <v>5000</v>
@@ -1732,7 +1732,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.1005871295929</v>
+        <v>2.10058689117432</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1761,7 +1761,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G48" t="n">
-        <v>2.11647367477417</v>
+        <v>2.11647391319275</v>
       </c>
       <c r="H48" t="n">
         <v>45500</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823916435242</v>
+        <v>2.11823892593384</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1877,7 +1877,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G52" t="n">
-        <v>2.15177798271179</v>
+        <v>2.15177774429321</v>
       </c>
       <c r="H52" t="n">
         <v>6500</v>
@@ -1935,7 +1935,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.12000417709351</v>
+        <v>2.12000393867493</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>2.43600010871887</v>
       </c>
       <c r="G55" t="n">
-        <v>2.15001249313354</v>
+        <v>2.15001273155212</v>
       </c>
       <c r="H55" t="n">
         <v>4000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824724197388</v>
+        <v>2.14824748039246</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.1270649433136</v>
+        <v>2.12706518173218</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2051,7 +2051,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13589096069336</v>
+        <v>2.13589119911194</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530800819397</v>
+        <v>2.15530824661255</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2138,7 +2138,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17296028137207</v>
+        <v>2.17296004295349</v>
       </c>
       <c r="H61" t="n">
         <v>15500</v>
@@ -2167,7 +2167,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828098297119</v>
+        <v>2.26828074455261</v>
       </c>
       <c r="H62" t="n">
         <v>12000</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300209999084</v>
+        <v>2.32300186157227</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709012985229</v>
+        <v>2.21709036827087</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534174919128</v>
+        <v>2.27534151077271</v>
       </c>
       <c r="H69" t="n">
         <v>6500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536717414856</v>
+        <v>2.36536693572998</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2602,7 +2602,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.59484267234802</v>
+        <v>2.5948429107666</v>
       </c>
       <c r="H77" t="n">
         <v>59000</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.71664142608643</v>
+        <v>2.716641664505</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2718,7 +2718,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G81" t="n">
-        <v>2.72723245620728</v>
+        <v>2.72723269462585</v>
       </c>
       <c r="H81" t="n">
         <v>19500</v>
@@ -2950,7 +2950,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H89" t="n">
         <v>12000</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3066,7 +3066,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G93" t="n">
-        <v>2.62582850456238</v>
+        <v>2.62582874298096</v>
       </c>
       <c r="H93" t="n">
         <v>5500</v>
@@ -3095,7 +3095,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G94" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H94" t="n">
         <v>3500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3298,7 +3298,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G101" t="n">
-        <v>2.5742335319519</v>
+        <v>2.57423329353333</v>
       </c>
       <c r="H101" t="n">
         <v>23000</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789666175842</v>
+        <v>2.50789642333984</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3414,7 +3414,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G105" t="n">
-        <v>2.50605416297913</v>
+        <v>2.50605392456055</v>
       </c>
       <c r="H105" t="n">
         <v>15500</v>
@@ -3443,7 +3443,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H106" t="n">
         <v>14000</v>
@@ -3472,7 +3472,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G107" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G108" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H108" t="n">
         <v>1000</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -3733,7 +3733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H116" t="n">
         <v>27000</v>
@@ -3791,7 +3791,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H118" t="n">
         <v>21500</v>
@@ -3907,7 +3907,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G122" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H122" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G123" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H123" t="n">
         <v>1500</v>
@@ -3965,7 +3965,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H124" t="n">
         <v>13500</v>
@@ -3994,7 +3994,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H125" t="n">
         <v>44000</v>
@@ -4023,7 +4023,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H126" t="n">
         <v>38000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4139,7 +4139,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G130" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H130" t="n">
         <v>22500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4255,7 +4255,7 @@
         <v>2.39599990844727</v>
       </c>
       <c r="G134" t="n">
-        <v>2.20753860473633</v>
+        <v>2.20753884315491</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4284,7 +4284,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>2.25544834136963</v>
+        <v>2.25544857978821</v>
       </c>
       <c r="H135" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252779006958</v>
+        <v>2.17252802848816</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4487,7 +4487,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H142" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515684127808</v>
+        <v>2.16515707969666</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4603,7 +4603,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G146" t="n">
-        <v>2.22228002548218</v>
+        <v>2.22228026390076</v>
       </c>
       <c r="H146" t="n">
         <v>500</v>
@@ -4690,7 +4690,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G149" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H149" t="n">
         <v>16000</v>
@@ -4719,7 +4719,7 @@
         <v>2.62400007247925</v>
       </c>
       <c r="G150" t="n">
-        <v>2.41760516166687</v>
+        <v>2.41760492324829</v>
       </c>
       <c r="H150" t="n">
         <v>1000</v>
@@ -4893,7 +4893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G156" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H156" t="n">
         <v>7500</v>
@@ -5009,7 +5009,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102100372314</v>
+        <v>2.40102076530457</v>
       </c>
       <c r="H160" t="n">
         <v>3000</v>
@@ -5270,7 +5270,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G169" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H169" t="n">
         <v>3000</v>
@@ -5473,7 +5473,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G176" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>2.4539999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>2.26097679138184</v>
+        <v>2.26097655296326</v>
       </c>
       <c r="H178" t="n">
         <v>73000</v>
@@ -5676,7 +5676,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H184" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H185" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5821,7 +5821,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G188" t="n">
-        <v>2.23517942428589</v>
+        <v>2.23517918586731</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5850,7 +5850,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G189" t="n">
-        <v>2.19464015960693</v>
+        <v>2.19463992118835</v>
       </c>
       <c r="H189" t="n">
         <v>1000</v>
@@ -5879,7 +5879,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G190" t="n">
-        <v>2.19279742240906</v>
+        <v>2.19279718399048</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5937,7 +5937,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122431755066</v>
+        <v>2.21122407913208</v>
       </c>
       <c r="H192" t="n">
         <v>11500</v>
@@ -6024,7 +6024,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H195" t="n">
         <v>1500</v>
@@ -6053,7 +6053,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G196" t="n">
-        <v>2.34389734268188</v>
+        <v>2.34389758110046</v>
       </c>
       <c r="H196" t="n">
         <v>17000</v>
@@ -6082,7 +6082,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G197" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H197" t="n">
         <v>65000</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365005493164</v>
+        <v>2.39365029335022</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758305549622</v>
+        <v>2.34758281707764</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6372,7 +6372,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731318473816</v>
+        <v>2.32731342315674</v>
       </c>
       <c r="H207" t="n">
         <v>14000</v>
@@ -6401,7 +6401,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H208" t="n">
         <v>24500</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890863418579</v>
+        <v>2.37890887260437</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6488,7 +6488,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H211" t="n">
         <v>47500</v>
@@ -6517,7 +6517,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>2.49684047698975</v>
+        <v>2.49684071540833</v>
       </c>
       <c r="H212" t="n">
         <v>12500</v>
@@ -6575,7 +6575,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G214" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H214" t="n">
         <v>7500</v>
@@ -6604,7 +6604,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G215" t="n">
-        <v>2.38996481895447</v>
+        <v>2.38996458053589</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G220" t="n">
-        <v>2.38627910614014</v>
+        <v>2.38627934455872</v>
       </c>
       <c r="H220" t="n">
         <v>7500</v>
@@ -6836,7 +6836,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G223" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H223" t="n">
         <v>500</v>
@@ -6865,7 +6865,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G224" t="n">
-        <v>2.42866086959839</v>
+        <v>2.42866110801697</v>
       </c>
       <c r="H224" t="n">
         <v>2500</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497587203979</v>
+        <v>2.42497563362122</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G227" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H227" t="n">
         <v>8500</v>
@@ -6981,7 +6981,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G228" t="n">
-        <v>2.36785268783569</v>
+        <v>2.36785244941711</v>
       </c>
       <c r="H228" t="n">
         <v>4500</v>
@@ -7039,7 +7039,7 @@
         <v>2.59599995613098</v>
       </c>
       <c r="G230" t="n">
-        <v>2.39180731773376</v>
+        <v>2.39180755615234</v>
       </c>
       <c r="H230" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.50600004196167</v>
       </c>
       <c r="G232" t="n">
-        <v>2.30888676643372</v>
+        <v>2.30888652801514</v>
       </c>
       <c r="H232" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G237" t="n">
-        <v>2.22965097427368</v>
+        <v>2.22965121269226</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043752670288</v>
+        <v>2.22043776512146</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7358,7 +7358,7 @@
         <v>2.52800011634827</v>
       </c>
       <c r="G241" t="n">
-        <v>2.32915592193604</v>
+        <v>2.32915616035461</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729131698608</v>
+        <v>2.25729155540466</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7735,7 +7735,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34021234512329</v>
+        <v>2.34021210670471</v>
       </c>
       <c r="H254" t="n">
         <v>19000</v>
@@ -7822,7 +7822,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499773979187</v>
+        <v>2.49499797821045</v>
       </c>
       <c r="H257" t="n">
         <v>21000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054781913757</v>
+        <v>2.57054805755615</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -8025,7 +8025,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61477279663086</v>
+        <v>2.61477255821228</v>
       </c>
       <c r="H264" t="n">
         <v>20000</v>
@@ -8112,7 +8112,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G267" t="n">
-        <v>2.65715456008911</v>
+        <v>2.65715432167053</v>
       </c>
       <c r="H267" t="n">
         <v>17000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663716316223</v>
+        <v>2.68663692474365</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8286,7 +8286,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G273" t="n">
-        <v>2.64425539970398</v>
+        <v>2.6442551612854</v>
       </c>
       <c r="H273" t="n">
         <v>13000</v>
@@ -8402,7 +8402,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G277" t="n">
-        <v>2.60740184783936</v>
+        <v>2.60740160942078</v>
       </c>
       <c r="H277" t="n">
         <v>13000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346908569336</v>
+        <v>2.65346932411194</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8576,7 +8576,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G283" t="n">
-        <v>2.61845779418945</v>
+        <v>2.61845803260803</v>
       </c>
       <c r="H283" t="n">
         <v>3500</v>
@@ -8634,7 +8634,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G285" t="n">
-        <v>2.47657084465027</v>
+        <v>2.47657108306885</v>
       </c>
       <c r="H285" t="n">
         <v>8500</v>
@@ -8692,7 +8692,7 @@
         <v>2.73200011253357</v>
       </c>
       <c r="G287" t="n">
-        <v>2.5171103477478</v>
+        <v>2.51711010932922</v>
       </c>
       <c r="H287" t="n">
         <v>5000</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481677055359</v>
+        <v>2.75481653213501</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8895,7 +8895,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G294" t="n">
-        <v>2.78061437606812</v>
+        <v>2.78061413764954</v>
       </c>
       <c r="H294" t="n">
         <v>29000</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>3.10599994659424</v>
       </c>
       <c r="G305" t="n">
-        <v>2.86169266700745</v>
+        <v>2.86169242858887</v>
       </c>
       <c r="H305" t="n">
         <v>105000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616445541382</v>
+        <v>2.85616421699524</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088376998901</v>
+        <v>2.80088400840759</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245711326599</v>
+        <v>2.78245687484741</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9475,7 +9475,7 @@
         <v>3.07200002670288</v>
       </c>
       <c r="G314" t="n">
-        <v>2.83036708831787</v>
+        <v>2.83036684989929</v>
       </c>
       <c r="H314" t="n">
         <v>29500</v>
@@ -9591,7 +9591,7 @@
         <v>3.16400003433228</v>
       </c>
       <c r="G318" t="n">
-        <v>2.9151303768158</v>
+        <v>2.91513061523438</v>
       </c>
       <c r="H318" t="n">
         <v>29000</v>
@@ -9620,7 +9620,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>2.98515248298645</v>
+        <v>2.98515272140503</v>
       </c>
       <c r="H319" t="n">
         <v>51500</v>
@@ -9649,7 +9649,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G320" t="n">
-        <v>3.04780387878418</v>
+        <v>3.04780411720276</v>
       </c>
       <c r="H320" t="n">
         <v>33500</v>
@@ -9678,7 +9678,7 @@
         <v>3.34400010108948</v>
       </c>
       <c r="G321" t="n">
-        <v>3.08097219467163</v>
+        <v>3.08097243309021</v>
       </c>
       <c r="H321" t="n">
         <v>110500</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202837944031</v>
+        <v>3.09202861785889</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9765,7 +9765,7 @@
         <v>3.54800009727478</v>
       </c>
       <c r="G324" t="n">
-        <v>3.2689266204834</v>
+        <v>3.26892638206482</v>
       </c>
       <c r="H324" t="n">
         <v>81500</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.27076888084412</v>
+        <v>3.2707691192627</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9910,7 +9910,7 @@
         <v>3.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>3.13993811607361</v>
+        <v>3.13993835449219</v>
       </c>
       <c r="H329" t="n">
         <v>22000</v>
@@ -9939,7 +9939,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937722206116</v>
+        <v>3.02937698364258</v>
       </c>
       <c r="H330" t="n">
         <v>27500</v>
@@ -9968,7 +9968,7 @@
         <v>3.26399993896484</v>
       </c>
       <c r="G331" t="n">
-        <v>3.00726461410522</v>
+        <v>3.0072648525238</v>
       </c>
       <c r="H331" t="n">
         <v>10000</v>
@@ -10055,7 +10055,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G334" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H334" t="n">
         <v>24000</v>
@@ -10084,7 +10084,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G335" t="n">
-        <v>3.04964637756348</v>
+        <v>3.04964661598206</v>
       </c>
       <c r="H335" t="n">
         <v>9500</v>
@@ -10171,7 +10171,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G338" t="n">
-        <v>3.08650016784668</v>
+        <v>3.08650040626526</v>
       </c>
       <c r="H338" t="n">
         <v>52000</v>
@@ -10258,7 +10258,7 @@
         <v>3.5</v>
       </c>
       <c r="G341" t="n">
-        <v>3.22470164299011</v>
+        <v>3.22470188140869</v>
       </c>
       <c r="H341" t="n">
         <v>21500</v>
@@ -10345,7 +10345,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>3.11414051055908</v>
+        <v>3.11414074897766</v>
       </c>
       <c r="H344" t="n">
         <v>15500</v>
@@ -10519,7 +10519,7 @@
         <v>3.38800001144409</v>
       </c>
       <c r="G350" t="n">
-        <v>3.12151122093201</v>
+        <v>3.12151145935059</v>
       </c>
       <c r="H350" t="n">
         <v>7000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045527458191</v>
+        <v>3.11045503616333</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10577,7 +10577,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.03674793243408</v>
+        <v>3.0367476940155</v>
       </c>
       <c r="H352" t="n">
         <v>22000</v>
@@ -10693,7 +10693,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.2676408290863</v>
+        <v>3.26764059066772</v>
       </c>
       <c r="H356" t="n">
         <v>94000</v>
@@ -10838,7 +10838,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215264320374</v>
+        <v>3.29215288162231</v>
       </c>
       <c r="H361" t="n">
         <v>33000</v>
@@ -10867,7 +10867,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279147148132</v>
+        <v>3.18279123306274</v>
       </c>
       <c r="H362" t="n">
         <v>64000</v>
@@ -10954,7 +10954,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713475227356</v>
+        <v>3.17713451385498</v>
       </c>
       <c r="H365" t="n">
         <v>20500</v>
@@ -10983,7 +10983,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491179466248</v>
+        <v>3.11491203308105</v>
       </c>
       <c r="H366" t="n">
         <v>14500</v>
@@ -11302,7 +11302,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H377" t="n">
         <v>25500</v>
@@ -11447,7 +11447,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H382" t="n">
         <v>10500</v>
@@ -11563,7 +11563,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.9225869178772</v>
+        <v>2.92258667945862</v>
       </c>
       <c r="H386" t="n">
         <v>6000</v>
@@ -11592,7 +11592,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H389" t="n">
         <v>16000</v>
@@ -11708,7 +11708,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669528961182</v>
+        <v>2.98669505119324</v>
       </c>
       <c r="H391" t="n">
         <v>16000</v>
@@ -11824,7 +11824,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864707946777</v>
+        <v>2.88864684104919</v>
       </c>
       <c r="H395" t="n">
         <v>6500</v>
@@ -11853,7 +11853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144201278687</v>
+        <v>2.94144225120544</v>
       </c>
       <c r="H396" t="n">
         <v>6500</v>
@@ -11911,7 +11911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H399" t="n">
         <v>5000</v>
@@ -11969,7 +11969,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332790374756</v>
+        <v>2.94332766532898</v>
       </c>
       <c r="H400" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373134613037</v>
+        <v>2.90373158454895</v>
       </c>
       <c r="H406" t="n">
         <v>18000</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.8283097743988</v>
+        <v>2.82831001281738</v>
       </c>
       <c r="H409" t="n">
         <v>8500</v>
@@ -12346,7 +12346,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682827949524</v>
+        <v>2.78682804107666</v>
       </c>
       <c r="H413" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002665519714</v>
+        <v>2.80002689361572</v>
       </c>
       <c r="H414" t="n">
         <v>7000</v>
@@ -12462,7 +12462,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H417" t="n">
         <v>5500</v>
@@ -12694,7 +12694,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517753601074</v>
+        <v>2.71517777442932</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12752,7 +12752,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046611785889</v>
+        <v>2.99046635627747</v>
       </c>
       <c r="H427" t="n">
         <v>411000</v>
@@ -12839,7 +12839,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979150772095</v>
+        <v>2.86979174613953</v>
       </c>
       <c r="H430" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716534614563</v>
+        <v>2.84716510772705</v>
       </c>
       <c r="H434" t="n">
         <v>36000</v>
@@ -12984,7 +12984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H435" t="n">
         <v>18000</v>
@@ -13013,7 +13013,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659313201904</v>
+        <v>2.85659289360046</v>
       </c>
       <c r="H436" t="n">
         <v>2500</v>
@@ -13100,7 +13100,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430379867554</v>
+        <v>2.89430356025696</v>
       </c>
       <c r="H439" t="n">
         <v>82500</v>
@@ -13245,7 +13245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228563308716</v>
+        <v>3.09228539466858</v>
       </c>
       <c r="H444" t="n">
         <v>47000</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.0790867805481</v>
+        <v>3.07908654212952</v>
       </c>
       <c r="H446" t="n">
         <v>25500</v>
@@ -13390,7 +13390,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928566932678</v>
+        <v>2.77928590774536</v>
       </c>
       <c r="H449" t="n">
         <v>531500</v>
@@ -13506,7 +13506,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.45497298240662</v>
+        <v>2.4549732208252</v>
       </c>
       <c r="H453" t="n">
         <v>144500</v>
@@ -13535,7 +13535,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H454" t="n">
         <v>47000</v>
@@ -13593,7 +13593,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H456" t="n">
         <v>146500</v>
@@ -13680,7 +13680,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187652587891</v>
+        <v>2.57187628746033</v>
       </c>
       <c r="H459" t="n">
         <v>26500</v>
@@ -13738,7 +13738,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238236427307</v>
+        <v>2.66238212585449</v>
       </c>
       <c r="H461" t="n">
         <v>152500</v>
@@ -13767,7 +13767,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106892585754</v>
+        <v>2.65106916427612</v>
       </c>
       <c r="H462" t="n">
         <v>60000</v>
@@ -13825,7 +13825,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032793998718</v>
+        <v>2.63032817840576</v>
       </c>
       <c r="H464" t="n">
         <v>17500</v>
@@ -14173,7 +14173,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.5021116733551</v>
+        <v>2.50211143493652</v>
       </c>
       <c r="H476" t="n">
         <v>49500</v>
@@ -14202,7 +14202,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891282081604</v>
+        <v>2.48891258239746</v>
       </c>
       <c r="H477" t="n">
         <v>26500</v>
@@ -14231,7 +14231,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137068748474</v>
+        <v>2.48137044906616</v>
       </c>
       <c r="H478" t="n">
         <v>74500</v>
@@ -14289,7 +14289,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H480" t="n">
         <v>32000</v>
@@ -14492,7 +14492,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217804908752</v>
+        <v>2.40217781066895</v>
       </c>
       <c r="H487" t="n">
         <v>20000</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.52473783493042</v>
+        <v>2.524738073349</v>
       </c>
       <c r="H494" t="n">
         <v>26000</v>
@@ -14724,7 +14724,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399684906006</v>
+        <v>2.50399708747864</v>
       </c>
       <c r="H495" t="n">
         <v>14500</v>
@@ -14811,7 +14811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834036827087</v>
+        <v>2.49834060668945</v>
       </c>
       <c r="H498" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005701065063</v>
+        <v>2.47005724906921</v>
       </c>
       <c r="H499" t="n">
         <v>36500</v>
@@ -14898,7 +14898,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120191574097</v>
+        <v>2.45120167732239</v>
       </c>
       <c r="H501" t="n">
         <v>14500</v>
@@ -15043,7 +15043,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H506" t="n">
         <v>19000</v>
@@ -15217,7 +15217,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.31167197227478</v>
+        <v>2.3116717338562</v>
       </c>
       <c r="H512" t="n">
         <v>9500</v>
@@ -15449,7 +15449,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520789146423</v>
+        <v>2.38520812988281</v>
       </c>
       <c r="H520" t="n">
         <v>28500</v>
@@ -15652,7 +15652,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978631973267</v>
+        <v>2.30978655815125</v>
       </c>
       <c r="H530" t="n">
         <v>38000</v>
@@ -15797,7 +15797,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H532" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H533" t="n">
         <v>10000</v>
@@ -15855,7 +15855,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.290931224823</v>
+        <v>2.29093098640442</v>
       </c>
       <c r="H534" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207565307617</v>
+        <v>2.27207589149475</v>
       </c>
       <c r="H535" t="n">
         <v>23500</v>
@@ -15942,7 +15942,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H537" t="n">
         <v>39500</v>
@@ -16029,7 +16029,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H540" t="n">
         <v>27500</v>
@@ -16087,7 +16087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H542" t="n">
         <v>49000</v>
@@ -16145,7 +16145,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H544" t="n">
         <v>21500</v>
@@ -16203,7 +16203,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H546" t="n">
         <v>5500</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H547" t="n">
         <v>11500</v>
@@ -16261,7 +16261,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H548" t="n">
         <v>12000</v>
@@ -16319,7 +16319,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H550" t="n">
         <v>8000</v>
@@ -16406,7 +16406,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H553" t="n">
         <v>22500</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H559" t="n">
         <v>23500</v>
@@ -16667,7 +16667,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H562" t="n">
         <v>131000</v>
@@ -16696,7 +16696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H563" t="n">
         <v>9000</v>
@@ -16812,7 +16812,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035853385925</v>
+        <v>2.30035877227783</v>
       </c>
       <c r="H567" t="n">
         <v>101500</v>
@@ -16841,7 +16841,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264810562134</v>
+        <v>2.26264786720276</v>
       </c>
       <c r="H568" t="n">
         <v>69000</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H570" t="n">
         <v>27000</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722629547119</v>
+        <v>2.18722605705261</v>
       </c>
       <c r="H573" t="n">
         <v>18000</v>
@@ -17044,7 +17044,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H575" t="n">
         <v>27500</v>
@@ -17073,7 +17073,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837072372437</v>
+        <v>2.16837096214294</v>
       </c>
       <c r="H576" t="n">
         <v>19500</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894317626953</v>
+        <v>2.15894293785095</v>
       </c>
       <c r="H577" t="n">
         <v>31000</v>
@@ -17160,7 +17160,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H579" t="n">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066029548645</v>
+        <v>2.13066005706787</v>
       </c>
       <c r="H582" t="n">
         <v>21500</v>
@@ -17305,7 +17305,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H584" t="n">
         <v>3500</v>
@@ -17334,7 +17334,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123250961304</v>
+        <v>2.12123227119446</v>
       </c>
       <c r="H585" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H593" t="n">
         <v>18500</v>
@@ -17653,7 +17653,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H596" t="n">
         <v>20000</v>
@@ -17682,7 +17682,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.0552384853363</v>
+        <v>2.05523872375488</v>
       </c>
       <c r="H597" t="n">
         <v>13000</v>
@@ -17711,7 +17711,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581093788147</v>
+        <v>2.04581069946289</v>
       </c>
       <c r="H598" t="n">
         <v>45000</v>
@@ -17885,7 +17885,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038900852203</v>
+        <v>1.97038924694061</v>
       </c>
       <c r="H604" t="n">
         <v>50500</v>
@@ -18059,7 +18059,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082599639893</v>
+        <v>1.88082611560822</v>
       </c>
       <c r="H610" t="n">
         <v>29000</v>
@@ -80183,6 +80183,35 @@
         <v>600</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.323000013828278</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>2100</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TB.MI.xlsx
+++ b/data/TB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38478398323059</v>
+        <v>2.38478422164917</v>
       </c>
       <c r="H2" t="n">
         <v>35500</v>
@@ -456,7 +456,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38125348091125</v>
+        <v>2.38125371932983</v>
       </c>
       <c r="H3" t="n">
         <v>52000</v>
@@ -485,7 +485,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33182811737061</v>
+        <v>2.33182787895203</v>
       </c>
       <c r="H4" t="n">
         <v>5500</v>
@@ -514,7 +514,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G5" t="n">
-        <v>2.29652380943298</v>
+        <v>2.29652404785156</v>
       </c>
       <c r="H5" t="n">
         <v>20500</v>
@@ -543,7 +543,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G6" t="n">
-        <v>2.37419295310974</v>
+        <v>2.37419271469116</v>
       </c>
       <c r="H6" t="n">
         <v>20000</v>
@@ -572,7 +572,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H7" t="n">
         <v>27000</v>
@@ -601,7 +601,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34771490097046</v>
+        <v>2.34771513938904</v>
       </c>
       <c r="H8" t="n">
         <v>23500</v>
@@ -659,7 +659,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G10" t="n">
-        <v>2.37595772743225</v>
+        <v>2.37595820426941</v>
       </c>
       <c r="H10" t="n">
         <v>29000</v>
@@ -688,7 +688,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G11" t="n">
-        <v>2.29828953742981</v>
+        <v>2.29828929901123</v>
       </c>
       <c r="H11" t="n">
         <v>26500</v>
@@ -746,7 +746,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29299378395081</v>
+        <v>2.29299354553223</v>
       </c>
       <c r="H13" t="n">
         <v>49000</v>
@@ -775,7 +775,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22415089607239</v>
+        <v>2.22415065765381</v>
       </c>
       <c r="H14" t="n">
         <v>43000</v>
@@ -804,7 +804,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G15" t="n">
-        <v>2.25062894821167</v>
+        <v>2.25062870979309</v>
       </c>
       <c r="H15" t="n">
         <v>27500</v>
@@ -920,7 +920,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29475855827332</v>
+        <v>2.29475903511047</v>
       </c>
       <c r="H19" t="n">
         <v>1500</v>
@@ -949,7 +949,7 @@
         <v>2.41599988937378</v>
       </c>
       <c r="G20" t="n">
-        <v>2.13236045837402</v>
+        <v>2.1323606967926</v>
       </c>
       <c r="H20" t="n">
         <v>35000</v>
@@ -978,7 +978,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G21" t="n">
-        <v>2.18884706497192</v>
+        <v>2.18884682655334</v>
       </c>
       <c r="H21" t="n">
         <v>39000</v>
@@ -1007,7 +1007,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G22" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H22" t="n">
         <v>6000</v>
@@ -1036,7 +1036,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G23" t="n">
-        <v>2.17825555801392</v>
+        <v>2.1782557964325</v>
       </c>
       <c r="H23" t="n">
         <v>16000</v>
@@ -1065,7 +1065,7 @@
         <v>2.41799998283386</v>
       </c>
       <c r="G24" t="n">
-        <v>2.13412570953369</v>
+        <v>2.13412547111511</v>
       </c>
       <c r="H24" t="n">
         <v>17000</v>
@@ -1094,7 +1094,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G25" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H25" t="n">
         <v>6000</v>
@@ -1181,7 +1181,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91347599029541</v>
+        <v>1.91347587108612</v>
       </c>
       <c r="H28" t="n">
         <v>32500</v>
@@ -1239,7 +1239,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G30" t="n">
-        <v>1.7793208360672</v>
+        <v>1.77932071685791</v>
       </c>
       <c r="H30" t="n">
         <v>130500</v>
@@ -1268,7 +1268,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G31" t="n">
-        <v>1.75990343093872</v>
+        <v>1.75990355014801</v>
       </c>
       <c r="H31" t="n">
         <v>186500</v>
@@ -1355,7 +1355,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G34" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H34" t="n">
         <v>70500</v>
@@ -1442,7 +1442,7 @@
         <v>2.49399995803833</v>
       </c>
       <c r="G37" t="n">
-        <v>2.20120334625244</v>
+        <v>2.20120358467102</v>
       </c>
       <c r="H37" t="n">
         <v>23500</v>
@@ -1471,7 +1471,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.15354299545288</v>
+        <v>2.1535427570343</v>
       </c>
       <c r="H38" t="n">
         <v>21000</v>
@@ -1558,7 +1558,7 @@
         <v>2.33800005912781</v>
       </c>
       <c r="G41" t="n">
-        <v>2.06351780891418</v>
+        <v>2.06351804733276</v>
       </c>
       <c r="H41" t="n">
         <v>9500</v>
@@ -1587,7 +1587,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G42" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H42" t="n">
         <v>6500</v>
@@ -1616,7 +1616,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H43" t="n">
         <v>16000</v>
@@ -1645,7 +1645,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G44" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H44" t="n">
         <v>4000</v>
@@ -1703,7 +1703,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G46" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H46" t="n">
         <v>5000</v>
@@ -1732,7 +1732,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G47" t="n">
-        <v>2.10058689117432</v>
+        <v>2.1005871295929</v>
       </c>
       <c r="H47" t="n">
         <v>10000</v>
@@ -1790,7 +1790,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G49" t="n">
-        <v>2.11823892593384</v>
+        <v>2.11823916435242</v>
       </c>
       <c r="H49" t="n">
         <v>1500</v>
@@ -1819,7 +1819,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G50" t="n">
-        <v>2.07410907745361</v>
+        <v>2.07410883903503</v>
       </c>
       <c r="H50" t="n">
         <v>11500</v>
@@ -1935,7 +1935,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G54" t="n">
-        <v>2.12000393867493</v>
+        <v>2.12000417709351</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1993,7 +1993,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14824748039246</v>
+        <v>2.14824724197388</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2022,7 +2022,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G57" t="n">
-        <v>2.12706518173218</v>
+        <v>2.1270649433136</v>
       </c>
       <c r="H57" t="n">
         <v>12000</v>
@@ -2051,7 +2051,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>2.13589119911194</v>
+        <v>2.13589096069336</v>
       </c>
       <c r="H58" t="n">
         <v>2000</v>
@@ -2080,7 +2080,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G59" t="n">
-        <v>2.15530824661255</v>
+        <v>2.15530800819397</v>
       </c>
       <c r="H59" t="n">
         <v>113000</v>
@@ -2109,7 +2109,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G60" t="n">
-        <v>2.14648222923279</v>
+        <v>2.14648199081421</v>
       </c>
       <c r="H60" t="n">
         <v>1000</v>
@@ -2167,7 +2167,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26828074455261</v>
+        <v>2.26828098297119</v>
       </c>
       <c r="H62" t="n">
         <v>12000</v>
@@ -2254,7 +2254,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G65" t="n">
-        <v>2.32300186157227</v>
+        <v>2.32300233840942</v>
       </c>
       <c r="H65" t="n">
         <v>3000</v>
@@ -2283,7 +2283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G66" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H66" t="n">
         <v>6500</v>
@@ -2312,7 +2312,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G67" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>2.51200008392334</v>
       </c>
       <c r="G68" t="n">
-        <v>2.21709036827087</v>
+        <v>2.21709012985229</v>
       </c>
       <c r="H68" t="n">
         <v>14000</v>
@@ -2370,7 +2370,7 @@
         <v>2.57800006866455</v>
       </c>
       <c r="G69" t="n">
-        <v>2.27534151077271</v>
+        <v>2.27534174919128</v>
       </c>
       <c r="H69" t="n">
         <v>6500</v>
@@ -2399,7 +2399,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G70" t="n">
-        <v>2.23297715187073</v>
+        <v>2.23297667503357</v>
       </c>
       <c r="H70" t="n">
         <v>4500</v>
@@ -2428,7 +2428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36536693572998</v>
+        <v>2.36536717414856</v>
       </c>
       <c r="H71" t="n">
         <v>66500</v>
@@ -2457,7 +2457,7 @@
         <v>2.83800005912781</v>
       </c>
       <c r="G72" t="n">
-        <v>2.50481772422791</v>
+        <v>2.50481748580933</v>
       </c>
       <c r="H72" t="n">
         <v>185500</v>
@@ -2486,7 +2486,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G73" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H73" t="n">
         <v>62000</v>
@@ -2515,7 +2515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52423477172852</v>
+        <v>2.52423453330994</v>
       </c>
       <c r="H74" t="n">
         <v>54500</v>
@@ -2544,7 +2544,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G75" t="n">
-        <v>2.57542562484741</v>
+        <v>2.57542538642883</v>
       </c>
       <c r="H75" t="n">
         <v>29500</v>
@@ -2660,7 +2660,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G79" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H79" t="n">
         <v>63500</v>
@@ -2689,7 +2689,7 @@
         <v>3.07800006866455</v>
       </c>
       <c r="G80" t="n">
-        <v>2.716641664505</v>
+        <v>2.71664190292358</v>
       </c>
       <c r="H80" t="n">
         <v>3500</v>
@@ -2979,7 +2979,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G90" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H90" t="n">
         <v>9500</v>
@@ -3037,7 +3037,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G92" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H92" t="n">
         <v>14500</v>
@@ -3124,7 +3124,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G95" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H95" t="n">
         <v>17000</v>
@@ -3153,7 +3153,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G96" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H96" t="n">
         <v>22500</v>
@@ -3182,7 +3182,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G97" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H97" t="n">
         <v>500</v>
@@ -3211,7 +3211,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H98" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>2.75</v>
       </c>
       <c r="G100" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H100" t="n">
         <v>1500</v>
@@ -3385,7 +3385,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G104" t="n">
-        <v>2.50789642333984</v>
+        <v>2.50789666175842</v>
       </c>
       <c r="H104" t="n">
         <v>500</v>
@@ -3559,7 +3559,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G110" t="n">
-        <v>2.47841382026672</v>
+        <v>2.47841358184814</v>
       </c>
       <c r="H110" t="n">
         <v>3000</v>
@@ -3646,7 +3646,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>2.45998668670654</v>
+        <v>2.45998692512512</v>
       </c>
       <c r="H113" t="n">
         <v>1500</v>
@@ -3675,7 +3675,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G114" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H114" t="n">
         <v>27500</v>
@@ -3704,7 +3704,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G115" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H115" t="n">
         <v>24500</v>
@@ -3733,7 +3733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H116" t="n">
         <v>27000</v>
@@ -3791,7 +3791,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H118" t="n">
         <v>21500</v>
@@ -3965,7 +3965,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H124" t="n">
         <v>13500</v>
@@ -4023,7 +4023,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G126" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H126" t="n">
         <v>38000</v>
@@ -4052,7 +4052,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G127" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H127" t="n">
         <v>31500</v>
@@ -4110,7 +4110,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G129" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H129" t="n">
         <v>16500</v>
@@ -4226,7 +4226,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G133" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H133" t="n">
         <v>12500</v>
@@ -4371,7 +4371,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G138" t="n">
-        <v>2.25913381576538</v>
+        <v>2.25913405418396</v>
       </c>
       <c r="H138" t="n">
         <v>1000</v>
@@ -4400,7 +4400,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G139" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H139" t="n">
         <v>8500</v>
@@ -4429,7 +4429,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17252802848816</v>
+        <v>2.17252779006958</v>
       </c>
       <c r="H140" t="n">
         <v>3500</v>
@@ -4458,7 +4458,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G141" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G143" t="n">
-        <v>2.16515707969666</v>
+        <v>2.16515684127808</v>
       </c>
       <c r="H143" t="n">
         <v>3500</v>
@@ -4835,7 +4835,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G154" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H154" t="n">
         <v>2500</v>
@@ -4864,7 +4864,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G155" t="n">
-        <v>2.4341893196106</v>
+        <v>2.43418908119202</v>
       </c>
       <c r="H155" t="n">
         <v>4500</v>
@@ -5009,7 +5009,7 @@
         <v>2.60599994659424</v>
       </c>
       <c r="G160" t="n">
-        <v>2.40102076530457</v>
+        <v>2.40102100372314</v>
       </c>
       <c r="H160" t="n">
         <v>3000</v>
@@ -5038,7 +5038,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G161" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H161" t="n">
         <v>3500</v>
@@ -5067,7 +5067,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G162" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G167" t="n">
-        <v>2.33099889755249</v>
+        <v>2.33099865913391</v>
       </c>
       <c r="H167" t="n">
         <v>9500</v>
@@ -5357,7 +5357,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H172" t="n">
         <v>21000</v>
@@ -5386,7 +5386,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G173" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H173" t="n">
         <v>11000</v>
@@ -5415,7 +5415,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G174" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H174" t="n">
         <v>3500</v>
@@ -5560,7 +5560,7 @@
         <v>2.39199995994568</v>
       </c>
       <c r="G179" t="n">
-        <v>2.20385336875916</v>
+        <v>2.20385313034058</v>
       </c>
       <c r="H179" t="n">
         <v>11000</v>
@@ -5589,7 +5589,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G180" t="n">
-        <v>2.24807786941528</v>
+        <v>2.2480776309967</v>
       </c>
       <c r="H180" t="n">
         <v>43000</v>
@@ -5676,7 +5676,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G183" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H183" t="n">
         <v>6000</v>
@@ -5705,7 +5705,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G184" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H184" t="n">
         <v>2000</v>
@@ -5734,7 +5734,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H185" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G186" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H186" t="n">
         <v>1500</v>
@@ -5792,7 +5792,7 @@
         <v>2.43199992179871</v>
       </c>
       <c r="G187" t="n">
-        <v>2.24070715904236</v>
+        <v>2.24070692062378</v>
       </c>
       <c r="H187" t="n">
         <v>4500</v>
@@ -5908,7 +5908,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G191" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H191" t="n">
         <v>5000</v>
@@ -5937,7 +5937,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G192" t="n">
-        <v>2.21122407913208</v>
+        <v>2.21122431755066</v>
       </c>
       <c r="H192" t="n">
         <v>11500</v>
@@ -6111,7 +6111,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G198" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H198" t="n">
         <v>20000</v>
@@ -6198,7 +6198,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G201" t="n">
-        <v>2.39365029335022</v>
+        <v>2.39365005493164</v>
       </c>
       <c r="H201" t="n">
         <v>1000</v>
@@ -6285,7 +6285,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G204" t="n">
-        <v>2.34758281707764</v>
+        <v>2.34758305549622</v>
       </c>
       <c r="H204" t="n">
         <v>9500</v>
@@ -6372,7 +6372,7 @@
         <v>2.52600002288818</v>
       </c>
       <c r="G207" t="n">
-        <v>2.32731342315674</v>
+        <v>2.32731366157532</v>
       </c>
       <c r="H207" t="n">
         <v>14000</v>
@@ -6430,7 +6430,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G209" t="n">
-        <v>2.37890887260437</v>
+        <v>2.37890863418579</v>
       </c>
       <c r="H209" t="n">
         <v>12500</v>
@@ -6459,7 +6459,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G210" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H210" t="n">
         <v>13500</v>
@@ -6488,7 +6488,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G211" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H211" t="n">
         <v>47500</v>
@@ -6546,7 +6546,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4415602684021</v>
+        <v>2.44156002998352</v>
       </c>
       <c r="H213" t="n">
         <v>8000</v>
@@ -6778,7 +6778,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G221" t="n">
-        <v>2.37338066101074</v>
+        <v>2.37338042259216</v>
       </c>
       <c r="H221" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G225" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H225" t="n">
         <v>2000</v>
@@ -6923,7 +6923,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G226" t="n">
-        <v>2.42497563362122</v>
+        <v>2.42497587203979</v>
       </c>
       <c r="H226" t="n">
         <v>500</v>
@@ -7010,7 +7010,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G229" t="n">
-        <v>2.39549255371094</v>
+        <v>2.39549279212952</v>
       </c>
       <c r="H229" t="n">
         <v>9000</v>
@@ -7126,7 +7126,7 @@
         <v>2.5239999294281</v>
       </c>
       <c r="G233" t="n">
-        <v>2.32547068595886</v>
+        <v>2.32547044754028</v>
       </c>
       <c r="H233" t="n">
         <v>4500</v>
@@ -7184,7 +7184,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G235" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H235" t="n">
         <v>12500</v>
@@ -7213,7 +7213,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G236" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G238" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H238" t="n">
         <v>4000</v>
@@ -7300,7 +7300,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G239" t="n">
-        <v>2.22043776512146</v>
+        <v>2.22043752670288</v>
       </c>
       <c r="H239" t="n">
         <v>1000</v>
@@ -7474,7 +7474,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G245" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H245" t="n">
         <v>5000</v>
@@ -7590,7 +7590,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G249" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H249" t="n">
         <v>2500</v>
@@ -7648,7 +7648,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G251" t="n">
-        <v>2.25729155540466</v>
+        <v>2.25729131698608</v>
       </c>
       <c r="H251" t="n">
         <v>6500</v>
@@ -7793,7 +7793,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.41391968727112</v>
+        <v>2.41391944885254</v>
       </c>
       <c r="H256" t="n">
         <v>26000</v>
@@ -7822,7 +7822,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G257" t="n">
-        <v>2.49499797821045</v>
+        <v>2.49499773979187</v>
       </c>
       <c r="H257" t="n">
         <v>21000</v>
@@ -7938,7 +7938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>2.57054805755615</v>
+        <v>2.57054781913757</v>
       </c>
       <c r="H261" t="n">
         <v>38000</v>
@@ -7967,7 +7967,7 @@
         <v>2.7720000743866</v>
       </c>
       <c r="G262" t="n">
-        <v>2.55396389961243</v>
+        <v>2.55396413803101</v>
       </c>
       <c r="H262" t="n">
         <v>6500</v>
@@ -8054,7 +8054,7 @@
         <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H265" t="n">
         <v>121000</v>
@@ -8199,7 +8199,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G270" t="n">
-        <v>2.68663692474365</v>
+        <v>2.68663716316223</v>
       </c>
       <c r="H270" t="n">
         <v>9500</v>
@@ -8228,7 +8228,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G271" t="n">
-        <v>2.68848013877869</v>
+        <v>2.68847990036011</v>
       </c>
       <c r="H271" t="n">
         <v>8500</v>
@@ -8344,7 +8344,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G275" t="n">
-        <v>2.57976150512695</v>
+        <v>2.57976126670837</v>
       </c>
       <c r="H275" t="n">
         <v>20000</v>
@@ -8460,7 +8460,7 @@
         <v>2.76399993896484</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5465931892395</v>
+        <v>2.54659295082092</v>
       </c>
       <c r="H279" t="n">
         <v>3000</v>
@@ -8547,7 +8547,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G282" t="n">
-        <v>2.65346932411194</v>
+        <v>2.65346908569336</v>
       </c>
       <c r="H282" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>2.75</v>
       </c>
       <c r="G286" t="n">
-        <v>2.53369426727295</v>
+        <v>2.53369450569153</v>
       </c>
       <c r="H286" t="n">
         <v>4500</v>
@@ -8837,7 +8837,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H292" t="n">
         <v>23000</v>
@@ -8866,7 +8866,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>2.75481653213501</v>
+        <v>2.75481677055359</v>
       </c>
       <c r="H293" t="n">
         <v>6500</v>
@@ -8924,7 +8924,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G295" t="n">
-        <v>2.72349119186401</v>
+        <v>2.72349143028259</v>
       </c>
       <c r="H295" t="n">
         <v>13500</v>
@@ -9040,7 +9040,7 @@
         <v>3</v>
       </c>
       <c r="G299" t="n">
-        <v>2.76403021812439</v>
+        <v>2.76402997970581</v>
       </c>
       <c r="H299" t="n">
         <v>8500</v>
@@ -9069,7 +9069,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H300" t="n">
         <v>6500</v>
@@ -9098,7 +9098,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H301" t="n">
         <v>18000</v>
@@ -9127,7 +9127,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H302" t="n">
         <v>17000</v>
@@ -9156,7 +9156,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G303" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H303" t="n">
         <v>2000</v>
@@ -9243,7 +9243,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>2.85616421699524</v>
+        <v>2.85616445541382</v>
       </c>
       <c r="H306" t="n">
         <v>11000</v>
@@ -9330,7 +9330,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.80088400840759</v>
+        <v>2.80088376998901</v>
       </c>
       <c r="H309" t="n">
         <v>14500</v>
@@ -9388,7 +9388,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G311" t="n">
-        <v>2.78245687484741</v>
+        <v>2.78245711326599</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9504,7 +9504,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G315" t="n">
-        <v>2.80456924438477</v>
+        <v>2.80456900596619</v>
       </c>
       <c r="H315" t="n">
         <v>24000</v>
@@ -9562,7 +9562,7 @@
         <v>3.09200000762939</v>
       </c>
       <c r="G317" t="n">
-        <v>2.84879374504089</v>
+        <v>2.84879350662231</v>
       </c>
       <c r="H317" t="n">
         <v>8000</v>
@@ -9707,7 +9707,7 @@
         <v>3.35599994659424</v>
       </c>
       <c r="G322" t="n">
-        <v>3.09202861785889</v>
+        <v>3.09202837944031</v>
       </c>
       <c r="H322" t="n">
         <v>50000</v>
@@ -9794,7 +9794,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G325" t="n">
-        <v>3.2707691192627</v>
+        <v>3.27076888084412</v>
       </c>
       <c r="H325" t="n">
         <v>46500</v>
@@ -9939,7 +9939,7 @@
         <v>3.28800010681152</v>
       </c>
       <c r="G330" t="n">
-        <v>3.02937698364258</v>
+        <v>3.02937722206116</v>
       </c>
       <c r="H330" t="n">
         <v>27500</v>
@@ -9997,7 +9997,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G332" t="n">
-        <v>2.94461345672607</v>
+        <v>2.94461369514465</v>
       </c>
       <c r="H332" t="n">
         <v>23000</v>
@@ -10026,7 +10026,7 @@
         <v>3.24600005149841</v>
       </c>
       <c r="G333" t="n">
-        <v>2.99068069458008</v>
+        <v>2.9906804561615</v>
       </c>
       <c r="H333" t="n">
         <v>5500</v>
@@ -10113,7 +10113,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G336" t="n">
-        <v>3.05886006355286</v>
+        <v>3.05885982513428</v>
       </c>
       <c r="H336" t="n">
         <v>21500</v>
@@ -10461,7 +10461,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>3.15099430084229</v>
+        <v>3.15099453926086</v>
       </c>
       <c r="H348" t="n">
         <v>9500</v>
@@ -10490,7 +10490,7 @@
         <v>3.40199995040894</v>
       </c>
       <c r="G349" t="n">
-        <v>3.13441014289856</v>
+        <v>3.13441038131714</v>
       </c>
       <c r="H349" t="n">
         <v>16000</v>
@@ -10548,7 +10548,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G351" t="n">
-        <v>3.11045503616333</v>
+        <v>3.11045527458191</v>
       </c>
       <c r="H351" t="n">
         <v>11500</v>
@@ -10577,7 +10577,7 @@
         <v>3.2960000038147</v>
       </c>
       <c r="G352" t="n">
-        <v>3.0367476940155</v>
+        <v>3.03674793243408</v>
       </c>
       <c r="H352" t="n">
         <v>22000</v>
@@ -10693,7 +10693,7 @@
         <v>3.46600008010864</v>
       </c>
       <c r="G356" t="n">
-        <v>3.26764059066772</v>
+        <v>3.2676408290863</v>
       </c>
       <c r="H356" t="n">
         <v>94000</v>
@@ -10838,7 +10838,7 @@
         <v>3.49200010299683</v>
       </c>
       <c r="G361" t="n">
-        <v>3.29215288162231</v>
+        <v>3.29215264320374</v>
       </c>
       <c r="H361" t="n">
         <v>33000</v>
@@ -10867,7 +10867,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G362" t="n">
-        <v>3.18279123306274</v>
+        <v>3.18279147148132</v>
       </c>
       <c r="H362" t="n">
         <v>64000</v>
@@ -10954,7 +10954,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G365" t="n">
-        <v>3.17713451385498</v>
+        <v>3.17713475227356</v>
       </c>
       <c r="H365" t="n">
         <v>20500</v>
@@ -10983,7 +10983,7 @@
         <v>3.30399990081787</v>
       </c>
       <c r="G366" t="n">
-        <v>3.11491203308105</v>
+        <v>3.11491179466248</v>
       </c>
       <c r="H366" t="n">
         <v>14500</v>
@@ -11302,7 +11302,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G377" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H377" t="n">
         <v>25500</v>
@@ -11447,7 +11447,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G382" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H382" t="n">
         <v>10500</v>
@@ -11563,7 +11563,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G386" t="n">
-        <v>2.92258667945862</v>
+        <v>2.9225869178772</v>
       </c>
       <c r="H386" t="n">
         <v>6000</v>
@@ -11592,7 +11592,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G387" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H387" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H389" t="n">
         <v>16000</v>
@@ -11708,7 +11708,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G391" t="n">
-        <v>2.98669505119324</v>
+        <v>2.98669528961182</v>
       </c>
       <c r="H391" t="n">
         <v>16000</v>
@@ -11824,7 +11824,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G395" t="n">
-        <v>2.88864684104919</v>
+        <v>2.88864707946777</v>
       </c>
       <c r="H395" t="n">
         <v>6500</v>
@@ -11853,7 +11853,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G396" t="n">
-        <v>2.94144225120544</v>
+        <v>2.94144201278687</v>
       </c>
       <c r="H396" t="n">
         <v>6500</v>
@@ -11911,7 +11911,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G399" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H399" t="n">
         <v>5000</v>
@@ -11969,7 +11969,7 @@
         <v>3.12199997901917</v>
       </c>
       <c r="G400" t="n">
-        <v>2.94332766532898</v>
+        <v>2.94332790374756</v>
       </c>
       <c r="H400" t="n">
         <v>13000</v>
@@ -12143,7 +12143,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G406" t="n">
-        <v>2.90373158454895</v>
+        <v>2.90373134613037</v>
       </c>
       <c r="H406" t="n">
         <v>18000</v>
@@ -12230,7 +12230,7 @@
         <v>3</v>
       </c>
       <c r="G409" t="n">
-        <v>2.82831001281738</v>
+        <v>2.8283097743988</v>
       </c>
       <c r="H409" t="n">
         <v>8500</v>
@@ -12346,7 +12346,7 @@
         <v>2.95600008964539</v>
       </c>
       <c r="G413" t="n">
-        <v>2.78682804107666</v>
+        <v>2.78682827949524</v>
       </c>
       <c r="H413" t="n">
         <v>4500</v>
@@ -12375,7 +12375,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G414" t="n">
-        <v>2.80002689361572</v>
+        <v>2.80002665519714</v>
       </c>
       <c r="H414" t="n">
         <v>7000</v>
@@ -12462,7 +12462,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H417" t="n">
         <v>5500</v>
@@ -12694,7 +12694,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G425" t="n">
-        <v>2.71517777442932</v>
+        <v>2.71517753601074</v>
       </c>
       <c r="H425" t="n">
         <v>11000</v>
@@ -12752,7 +12752,7 @@
         <v>3.17199993133545</v>
       </c>
       <c r="G427" t="n">
-        <v>2.99046635627747</v>
+        <v>2.99046611785889</v>
       </c>
       <c r="H427" t="n">
         <v>411000</v>
@@ -12839,7 +12839,7 @@
         <v>3.04399991035461</v>
       </c>
       <c r="G430" t="n">
-        <v>2.86979174613953</v>
+        <v>2.86979150772095</v>
       </c>
       <c r="H430" t="n">
         <v>10000</v>
@@ -12955,7 +12955,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>2.84716510772705</v>
+        <v>2.84716534614563</v>
       </c>
       <c r="H434" t="n">
         <v>36000</v>
@@ -12984,7 +12984,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G435" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H435" t="n">
         <v>18000</v>
@@ -13013,7 +13013,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G436" t="n">
-        <v>2.85659289360046</v>
+        <v>2.85659313201904</v>
       </c>
       <c r="H436" t="n">
         <v>2500</v>
@@ -13100,7 +13100,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G439" t="n">
-        <v>2.89430356025696</v>
+        <v>2.89430379867554</v>
       </c>
       <c r="H439" t="n">
         <v>82500</v>
@@ -13245,7 +13245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G444" t="n">
-        <v>3.09228539466858</v>
+        <v>3.09228563308716</v>
       </c>
       <c r="H444" t="n">
         <v>47000</v>
@@ -13303,7 +13303,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G446" t="n">
-        <v>3.07908654212952</v>
+        <v>3.0790867805481</v>
       </c>
       <c r="H446" t="n">
         <v>25500</v>
@@ -13390,7 +13390,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G449" t="n">
-        <v>2.77928590774536</v>
+        <v>2.77928566932678</v>
       </c>
       <c r="H449" t="n">
         <v>531500</v>
@@ -13506,7 +13506,7 @@
         <v>2.60400009155273</v>
       </c>
       <c r="G453" t="n">
-        <v>2.4549732208252</v>
+        <v>2.45497298240662</v>
       </c>
       <c r="H453" t="n">
         <v>144500</v>
@@ -13535,7 +13535,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H454" t="n">
         <v>47000</v>
@@ -13593,7 +13593,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G456" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H456" t="n">
         <v>146500</v>
@@ -13680,7 +13680,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G459" t="n">
-        <v>2.57187628746033</v>
+        <v>2.57187652587891</v>
       </c>
       <c r="H459" t="n">
         <v>26500</v>
@@ -13738,7 +13738,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G461" t="n">
-        <v>2.66238212585449</v>
+        <v>2.66238236427307</v>
       </c>
       <c r="H461" t="n">
         <v>152500</v>
@@ -13767,7 +13767,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G462" t="n">
-        <v>2.65106916427612</v>
+        <v>2.65106892585754</v>
       </c>
       <c r="H462" t="n">
         <v>60000</v>
@@ -13825,7 +13825,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>2.63032817840576</v>
+        <v>2.63032793998718</v>
       </c>
       <c r="H464" t="n">
         <v>17500</v>
@@ -14173,7 +14173,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G476" t="n">
-        <v>2.50211143493652</v>
+        <v>2.5021116733551</v>
       </c>
       <c r="H476" t="n">
         <v>49500</v>
@@ -14202,7 +14202,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G477" t="n">
-        <v>2.48891258239746</v>
+        <v>2.48891282081604</v>
       </c>
       <c r="H477" t="n">
         <v>26500</v>
@@ -14231,7 +14231,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>2.48137044906616</v>
+        <v>2.48137068748474</v>
       </c>
       <c r="H478" t="n">
         <v>74500</v>
@@ -14289,7 +14289,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G480" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H480" t="n">
         <v>32000</v>
@@ -14492,7 +14492,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G487" t="n">
-        <v>2.40217781066895</v>
+        <v>2.40217804908752</v>
       </c>
       <c r="H487" t="n">
         <v>20000</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.524738073349</v>
+        <v>2.52473783493042</v>
       </c>
       <c r="H494" t="n">
         <v>26000</v>
@@ -14724,7 +14724,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G495" t="n">
-        <v>2.50399708747864</v>
+        <v>2.50399684906006</v>
       </c>
       <c r="H495" t="n">
         <v>14500</v>
@@ -14811,7 +14811,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49834060668945</v>
+        <v>2.49834036827087</v>
       </c>
       <c r="H498" t="n">
         <v>8500</v>
@@ -14840,7 +14840,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G499" t="n">
-        <v>2.47005724906921</v>
+        <v>2.47005701065063</v>
       </c>
       <c r="H499" t="n">
         <v>36500</v>
@@ -14898,7 +14898,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G501" t="n">
-        <v>2.45120167732239</v>
+        <v>2.45120191574097</v>
       </c>
       <c r="H501" t="n">
         <v>14500</v>
@@ -15043,7 +15043,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G506" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H506" t="n">
         <v>19000</v>
@@ -15217,7 +15217,7 @@
         <v>2.45199990272522</v>
       </c>
       <c r="G512" t="n">
-        <v>2.3116717338562</v>
+        <v>2.31167197227478</v>
       </c>
       <c r="H512" t="n">
         <v>9500</v>
@@ -15449,7 +15449,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>2.38520812988281</v>
+        <v>2.38520789146423</v>
       </c>
       <c r="H520" t="n">
         <v>28500</v>
@@ -15652,7 +15652,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G527" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15739,7 +15739,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G530" t="n">
-        <v>2.30978655815125</v>
+        <v>2.30978631973267</v>
       </c>
       <c r="H530" t="n">
         <v>38000</v>
@@ -15797,7 +15797,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G532" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H532" t="n">
         <v>19000</v>
@@ -15826,7 +15826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G533" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H533" t="n">
         <v>10000</v>
@@ -15855,7 +15855,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G534" t="n">
-        <v>2.29093098640442</v>
+        <v>2.290931224823</v>
       </c>
       <c r="H534" t="n">
         <v>6000</v>
@@ -15884,7 +15884,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G535" t="n">
-        <v>2.27207589149475</v>
+        <v>2.27207565307617</v>
       </c>
       <c r="H535" t="n">
         <v>23500</v>
@@ -15942,7 +15942,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H537" t="n">
         <v>39500</v>
@@ -16029,7 +16029,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H540" t="n">
         <v>27500</v>
@@ -16087,7 +16087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G542" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H542" t="n">
         <v>49000</v>
@@ -16145,7 +16145,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H544" t="n">
         <v>21500</v>
@@ -16203,7 +16203,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H546" t="n">
         <v>5500</v>
@@ -16232,7 +16232,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H547" t="n">
         <v>11500</v>
@@ -16261,7 +16261,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H548" t="n">
         <v>12000</v>
@@ -16319,7 +16319,7 @@
         <v>2.25</v>
       </c>
       <c r="G550" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H550" t="n">
         <v>8000</v>
@@ -16406,7 +16406,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H553" t="n">
         <v>22500</v>
@@ -16580,7 +16580,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G559" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H559" t="n">
         <v>23500</v>
@@ -16667,7 +16667,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H562" t="n">
         <v>131000</v>
@@ -16696,7 +16696,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G563" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H563" t="n">
         <v>9000</v>
@@ -16812,7 +16812,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.30035877227783</v>
+        <v>2.30035853385925</v>
       </c>
       <c r="H567" t="n">
         <v>101500</v>
@@ -16841,7 +16841,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.26264786720276</v>
+        <v>2.26264810562134</v>
       </c>
       <c r="H568" t="n">
         <v>69000</v>
@@ -16899,7 +16899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G570" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H570" t="n">
         <v>27000</v>
@@ -16986,7 +16986,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.18722605705261</v>
+        <v>2.18722629547119</v>
       </c>
       <c r="H573" t="n">
         <v>18000</v>
@@ -17044,7 +17044,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G575" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H575" t="n">
         <v>27500</v>
@@ -17073,7 +17073,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G576" t="n">
-        <v>2.16837096214294</v>
+        <v>2.16837072372437</v>
       </c>
       <c r="H576" t="n">
         <v>19500</v>
@@ -17102,7 +17102,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G577" t="n">
-        <v>2.15894293785095</v>
+        <v>2.15894317626953</v>
       </c>
       <c r="H577" t="n">
         <v>31000</v>
@@ -17160,7 +17160,7 @@
         <v>2.25</v>
       </c>
       <c r="G579" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H579" t="n">
         <v>8000</v>
@@ -17247,7 +17247,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G582" t="n">
-        <v>2.13066005706787</v>
+        <v>2.13066029548645</v>
       </c>
       <c r="H582" t="n">
         <v>21500</v>
@@ -17305,7 +17305,7 @@
         <v>2.25</v>
       </c>
       <c r="G584" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H584" t="n">
         <v>3500</v>
@@ -17334,7 +17334,7 @@
         <v>2.25</v>
       </c>
       <c r="G585" t="n">
-        <v>2.12123227119446</v>
+        <v>2.12123250961304</v>
       </c>
       <c r="H585" t="n">
         <v>14000</v>
@@ -17566,7 +17566,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G593" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H593" t="n">
         <v>18500</v>
@@ -17653,7 +17653,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G596" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H596" t="n">
         <v>20000</v>
@@ -17682,7 +17682,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G597" t="n">
-        <v>2.05523872375488</v>
+        <v>2.0552384853363</v>
       </c>
       <c r="H597" t="n">
         <v>13000</v>
@@ -17711,7 +17711,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G598" t="n">
-        <v>2.04581069946289</v>
+        <v>2.04581093788147</v>
       </c>
       <c r="H598" t="n">
         <v>45000</v>
@@ -17885,7 +17885,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G604" t="n">
-        <v>1.97038924694061</v>
+        <v>1.97038900852203</v>
       </c>
       <c r="H604" t="n">
         <v>50500</v>
@@ -18059,7 +18059,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G610" t="n">
-        <v>1.88082611560822</v>
+        <v>1.88082599639893</v>
       </c>
       <c r="H610" t="n">
         <v>29000</v>
@@ -80197,7 +80197,7 @@
         <v>0.324999988079071</v>
       </c>
       <c r="D2753" t="n">
-        <v>0.324999988079071</v>
+        <v>0.33500000834465</v>
       </c>
       <c r="E2753" t="n">
         <v>0.323000013828278</v>
